--- a/research/traditional_assets/database/data/cyprus/cyprus_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_real_estate_operations_services.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07857194125249387</v>
+        <v>0.07851310132592823</v>
       </c>
       <c r="C2">
-        <v>852.2176830234428</v>
+        <v>845.9454754810556</v>
       </c>
       <c r="D2">
-        <v>808.8176830234428</v>
+        <v>810.2724754810556</v>
       </c>
       <c r="E2">
-        <v>-474.6</v>
+        <v>-466.873</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.727</v>
       </c>
       <c r="G2">
         <v>43.4</v>
@@ -1445,28 +1445,28 @@
         <v>45.075</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3886681</v>
       </c>
       <c r="N2">
-        <v>45.075</v>
+        <v>44.6863319</v>
       </c>
       <c r="O2">
-        <v>5.634374999999999</v>
+        <v>5.5857914875</v>
       </c>
       <c r="P2">
-        <v>39.440625</v>
+        <v>39.1005404125</v>
       </c>
       <c r="Q2">
-        <v>40.240625</v>
+        <v>39.9005404125</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07857194125249387</v>
+        <v>0.07886159224841235</v>
       </c>
       <c r="T2">
-        <v>0.5525820103960151</v>
+        <v>0.5574659423060808</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>115.9729856913907</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07851310132592823</v>
+        <v>0.07845426139936262</v>
       </c>
       <c r="C3">
-        <v>845.9454754810556</v>
+        <v>839.678510738701</v>
       </c>
       <c r="D3">
-        <v>810.2724754810556</v>
+        <v>811.732510738701</v>
       </c>
       <c r="E3">
-        <v>-466.873</v>
+        <v>-459.146</v>
       </c>
       <c r="F3">
-        <v>7.727</v>
+        <v>15.454</v>
       </c>
       <c r="G3">
         <v>43.4</v>
@@ -1527,28 +1527,28 @@
         <v>45.075</v>
       </c>
       <c r="M3">
-        <v>0.3886681</v>
+        <v>0.7773362</v>
       </c>
       <c r="N3">
-        <v>44.6863319</v>
+        <v>44.2976638</v>
       </c>
       <c r="O3">
-        <v>5.5857914875</v>
+        <v>5.537207974999999</v>
       </c>
       <c r="P3">
-        <v>39.1005404125</v>
+        <v>38.76045582499999</v>
       </c>
       <c r="Q3">
-        <v>39.9005404125</v>
+        <v>39.560455825</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07886159224841235</v>
+        <v>0.07915715448914554</v>
       </c>
       <c r="T3">
-        <v>0.5574659423060808</v>
+        <v>0.5624495462959439</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>115.9729856913907</v>
+        <v>57.98649284569533</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07845426139936262</v>
+        <v>0.078395421472797</v>
       </c>
       <c r="C4">
-        <v>839.678510738701</v>
+        <v>833.4168171886469</v>
       </c>
       <c r="D4">
-        <v>811.732510738701</v>
+        <v>813.1978171886469</v>
       </c>
       <c r="E4">
-        <v>-459.146</v>
+        <v>-451.419</v>
       </c>
       <c r="F4">
-        <v>15.454</v>
+        <v>23.181</v>
       </c>
       <c r="G4">
         <v>43.4</v>
@@ -1609,28 +1609,28 @@
         <v>45.075</v>
       </c>
       <c r="M4">
-        <v>0.7773362</v>
+        <v>1.1660043</v>
       </c>
       <c r="N4">
-        <v>44.2976638</v>
+        <v>43.9089957</v>
       </c>
       <c r="O4">
-        <v>5.537207974999999</v>
+        <v>5.4886244625</v>
       </c>
       <c r="P4">
-        <v>38.76045582499999</v>
+        <v>38.4203712375</v>
       </c>
       <c r="Q4">
-        <v>39.560455825</v>
+        <v>39.2203712375</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07915715448914554</v>
+        <v>0.07945881079669795</v>
       </c>
       <c r="T4">
-        <v>0.5624495462959439</v>
+        <v>0.5675359050072474</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>57.98649284569533</v>
+        <v>38.65766189713023</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.078395421472797</v>
+        <v>0.07833658154623138</v>
       </c>
       <c r="C5">
-        <v>833.4168171886469</v>
+        <v>827.1604234285408</v>
       </c>
       <c r="D5">
-        <v>813.1978171886469</v>
+        <v>814.6684234285408</v>
       </c>
       <c r="E5">
-        <v>-451.419</v>
+        <v>-443.692</v>
       </c>
       <c r="F5">
-        <v>23.181</v>
+        <v>30.908</v>
       </c>
       <c r="G5">
         <v>43.4</v>
@@ -1691,28 +1691,28 @@
         <v>45.075</v>
       </c>
       <c r="M5">
-        <v>1.1660043</v>
+        <v>1.5546724</v>
       </c>
       <c r="N5">
-        <v>43.9089957</v>
+        <v>43.52032759999999</v>
       </c>
       <c r="O5">
-        <v>5.4886244625</v>
+        <v>5.440040949999999</v>
       </c>
       <c r="P5">
-        <v>38.4203712375</v>
+        <v>38.08028665</v>
       </c>
       <c r="Q5">
-        <v>39.2203712375</v>
+        <v>38.88028665</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07945881079669795</v>
+        <v>0.07976675161065769</v>
       </c>
       <c r="T5">
-        <v>0.5675359050072474</v>
+        <v>0.5727282295250364</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.65766189713023</v>
+        <v>28.99324642284767</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07833658154623138</v>
+        <v>0.07827774161966576</v>
       </c>
       <c r="C6">
-        <v>827.1604234285408</v>
+        <v>820.909358263272</v>
       </c>
       <c r="D6">
-        <v>814.6684234285408</v>
+        <v>816.144358263272</v>
       </c>
       <c r="E6">
-        <v>-443.692</v>
+        <v>-435.965</v>
       </c>
       <c r="F6">
-        <v>30.908</v>
+        <v>38.63500000000001</v>
       </c>
       <c r="G6">
         <v>43.4</v>
@@ -1773,28 +1773,28 @@
         <v>45.075</v>
       </c>
       <c r="M6">
-        <v>1.5546724</v>
+        <v>1.9433405</v>
       </c>
       <c r="N6">
-        <v>43.52032759999999</v>
+        <v>43.1316595</v>
       </c>
       <c r="O6">
-        <v>5.440040949999999</v>
+        <v>5.3914574375</v>
       </c>
       <c r="P6">
-        <v>38.08028665</v>
+        <v>37.7402020625</v>
       </c>
       <c r="Q6">
-        <v>38.88028665</v>
+        <v>38.5402020625</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07976675161065769</v>
+        <v>0.08008117538912186</v>
       </c>
       <c r="T6">
-        <v>0.5727282295250364</v>
+        <v>0.5780298661379368</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.99324642284767</v>
+        <v>23.19459713827813</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07827774161966576</v>
+        <v>0.07821890169310015</v>
       </c>
       <c r="C7">
-        <v>820.909358263272</v>
+        <v>814.6636507068517</v>
       </c>
       <c r="D7">
-        <v>816.144358263272</v>
+        <v>817.6256507068517</v>
       </c>
       <c r="E7">
-        <v>-435.965</v>
+        <v>-428.238</v>
       </c>
       <c r="F7">
-        <v>38.63500000000001</v>
+        <v>46.36200000000001</v>
       </c>
       <c r="G7">
         <v>43.4</v>
@@ -1855,28 +1855,28 @@
         <v>45.075</v>
       </c>
       <c r="M7">
-        <v>1.9433405</v>
+        <v>2.3320086</v>
       </c>
       <c r="N7">
-        <v>43.1316595</v>
+        <v>42.74299139999999</v>
       </c>
       <c r="O7">
-        <v>5.3914574375</v>
+        <v>5.342873924999999</v>
       </c>
       <c r="P7">
-        <v>37.7402020625</v>
+        <v>37.40011747499999</v>
       </c>
       <c r="Q7">
-        <v>38.5402020625</v>
+        <v>38.200117475</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08008117538912186</v>
+        <v>0.08040228903521293</v>
       </c>
       <c r="T7">
-        <v>0.5780298661379368</v>
+        <v>0.5834443035298351</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.19459713827813</v>
+        <v>19.32883094856511</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07821890169310015</v>
+        <v>0.07816006176653455</v>
       </c>
       <c r="C8">
-        <v>814.6636507068517</v>
+        <v>808.4233299843154</v>
       </c>
       <c r="D8">
-        <v>817.6256507068517</v>
+        <v>819.1123299843154</v>
       </c>
       <c r="E8">
-        <v>-428.238</v>
+        <v>-420.511</v>
       </c>
       <c r="F8">
-        <v>46.362</v>
+        <v>54.089</v>
       </c>
       <c r="G8">
         <v>43.4</v>
@@ -1937,28 +1937,28 @@
         <v>45.075</v>
       </c>
       <c r="M8">
-        <v>2.3320086</v>
+        <v>2.7206767</v>
       </c>
       <c r="N8">
-        <v>42.74299139999999</v>
+        <v>42.3543233</v>
       </c>
       <c r="O8">
-        <v>5.342873924999999</v>
+        <v>5.2942904125</v>
       </c>
       <c r="P8">
-        <v>37.40011747499999</v>
+        <v>37.0600328875</v>
       </c>
       <c r="Q8">
-        <v>38.200117475</v>
+        <v>37.8600328875</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08040228903521293</v>
+        <v>0.08073030835111242</v>
       </c>
       <c r="T8">
-        <v>0.5834443035298351</v>
+        <v>0.5889751804355376</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.32883094856511</v>
+        <v>16.56756938448438</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07816006176653453</v>
+        <v>0.07810122183996893</v>
       </c>
       <c r="C9">
-        <v>808.4233299843156</v>
+        <v>802.1884255336432</v>
       </c>
       <c r="D9">
-        <v>819.1123299843157</v>
+        <v>820.6044255336433</v>
       </c>
       <c r="E9">
-        <v>-420.511</v>
+        <v>-412.784</v>
       </c>
       <c r="F9">
-        <v>54.08900000000001</v>
+        <v>61.816</v>
       </c>
       <c r="G9">
         <v>43.4</v>
@@ -2019,28 +2019,28 @@
         <v>45.075</v>
       </c>
       <c r="M9">
-        <v>2.7206767</v>
+        <v>3.1093448</v>
       </c>
       <c r="N9">
-        <v>42.3543233</v>
+        <v>41.96565519999999</v>
       </c>
       <c r="O9">
-        <v>5.2942904125</v>
+        <v>5.245706899999999</v>
       </c>
       <c r="P9">
-        <v>37.0600328875</v>
+        <v>36.71994829999999</v>
       </c>
       <c r="Q9">
-        <v>37.8600328875</v>
+        <v>37.5199483</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08073030835111242</v>
+        <v>0.08106545852170535</v>
       </c>
       <c r="T9">
-        <v>0.5889751804355376</v>
+        <v>0.594626293795712</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.56756938448438</v>
+        <v>14.49662321142383</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07810122183996893</v>
+        <v>0.07804238191340329</v>
       </c>
       <c r="C10">
-        <v>802.1884255336432</v>
+        <v>795.9589670077041</v>
       </c>
       <c r="D10">
-        <v>820.6044255336433</v>
+        <v>822.1019670077042</v>
       </c>
       <c r="E10">
-        <v>-412.784</v>
+        <v>-405.057</v>
       </c>
       <c r="F10">
-        <v>61.816</v>
+        <v>69.54300000000001</v>
       </c>
       <c r="G10">
         <v>43.4</v>
@@ -2101,28 +2101,28 @@
         <v>45.075</v>
       </c>
       <c r="M10">
-        <v>3.1093448</v>
+        <v>3.4980129</v>
       </c>
       <c r="N10">
-        <v>41.96565519999999</v>
+        <v>41.5769871</v>
       </c>
       <c r="O10">
-        <v>5.245706899999999</v>
+        <v>5.1971233875</v>
       </c>
       <c r="P10">
-        <v>36.71994829999999</v>
+        <v>36.3798637125</v>
       </c>
       <c r="Q10">
-        <v>37.5199483</v>
+        <v>37.1798637125</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08106545852170535</v>
+        <v>0.08140797463011351</v>
       </c>
       <c r="T10">
-        <v>0.594626293795712</v>
+        <v>0.6004016074495163</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.49662321142383</v>
+        <v>12.88588729904341</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07804238191340329</v>
+        <v>0.0781147919868377</v>
       </c>
       <c r="C11">
-        <v>795.9589670077041</v>
+        <v>786.3898241331393</v>
       </c>
       <c r="D11">
-        <v>822.1019670077042</v>
+        <v>820.2598241331393</v>
       </c>
       <c r="E11">
-        <v>-405.057</v>
+        <v>-397.33</v>
       </c>
       <c r="F11">
-        <v>69.54300000000001</v>
+        <v>77.27</v>
       </c>
       <c r="G11">
         <v>43.4</v>
@@ -2183,45 +2183,45 @@
         <v>45.075</v>
       </c>
       <c r="M11">
-        <v>3.4980129</v>
+        <v>4.002586</v>
       </c>
       <c r="N11">
-        <v>41.5769871</v>
+        <v>41.07241399999999</v>
       </c>
       <c r="O11">
-        <v>5.1971233875</v>
+        <v>5.134051749999999</v>
       </c>
       <c r="P11">
-        <v>36.3798637125</v>
+        <v>35.93836225</v>
       </c>
       <c r="Q11">
-        <v>37.1798637125</v>
+        <v>36.73836225</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08140797463011351</v>
+        <v>0.08175810220759744</v>
       </c>
       <c r="T11">
-        <v>0.6004016074495163</v>
+        <v>0.6063052614067388</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.0440125</v>
+        <v>0.045325</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>12.88588729904341</v>
+        <v>11.26146945999411</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0781147919868377</v>
+        <v>0.07806907706027207</v>
       </c>
       <c r="C12">
-        <v>786.3898241331393</v>
+        <v>779.8248690703077</v>
       </c>
       <c r="D12">
-        <v>820.2598241331393</v>
+        <v>821.4218690703077</v>
       </c>
       <c r="E12">
-        <v>-397.33</v>
+        <v>-389.603</v>
       </c>
       <c r="F12">
-        <v>77.27000000000001</v>
+        <v>84.997</v>
       </c>
       <c r="G12">
         <v>43.4</v>
@@ -2265,28 +2265,28 @@
         <v>45.075</v>
       </c>
       <c r="M12">
-        <v>4.002586000000001</v>
+        <v>4.4028446</v>
       </c>
       <c r="N12">
-        <v>41.07241399999999</v>
+        <v>40.67215539999999</v>
       </c>
       <c r="O12">
-        <v>5.134051749999999</v>
+        <v>5.084019424999999</v>
       </c>
       <c r="P12">
-        <v>35.93836225</v>
+        <v>35.58813597499999</v>
       </c>
       <c r="Q12">
-        <v>36.73836225</v>
+        <v>36.388135975</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08175810220759744</v>
+        <v>0.08211609782053042</v>
       </c>
       <c r="T12">
-        <v>0.6063052614067388</v>
+        <v>0.6123415817450224</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.26146945999411</v>
+        <v>10.23769950908556</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07806907706027207</v>
+        <v>0.07820186213370645</v>
       </c>
       <c r="C13">
-        <v>779.8248690703077</v>
+        <v>768.7316254033536</v>
       </c>
       <c r="D13">
-        <v>821.4218690703077</v>
+        <v>818.0556254033537</v>
       </c>
       <c r="E13">
-        <v>-389.603</v>
+        <v>-381.876</v>
       </c>
       <c r="F13">
-        <v>84.997</v>
+        <v>92.724</v>
       </c>
       <c r="G13">
         <v>43.4</v>
@@ -2347,45 +2347,45 @@
         <v>45.075</v>
       </c>
       <c r="M13">
-        <v>4.4028446</v>
+        <v>4.960734</v>
       </c>
       <c r="N13">
-        <v>40.67215539999999</v>
+        <v>40.11426599999999</v>
       </c>
       <c r="O13">
-        <v>5.084019424999999</v>
+        <v>5.014283249999999</v>
       </c>
       <c r="P13">
-        <v>35.58813597499999</v>
+        <v>35.09998275</v>
       </c>
       <c r="Q13">
-        <v>36.388135975</v>
+        <v>35.89998275</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08211609782053042</v>
+        <v>0.08248222969739369</v>
       </c>
       <c r="T13">
-        <v>0.6123415817450224</v>
+        <v>0.6185150911819033</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.045325</v>
+        <v>0.0468125</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.23769950908556</v>
+        <v>9.086356978624533</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07820186213370645</v>
+        <v>0.07817102220714083</v>
       </c>
       <c r="C14">
-        <v>768.7316254033536</v>
+        <v>761.783988354965</v>
       </c>
       <c r="D14">
-        <v>818.0556254033537</v>
+        <v>818.834988354965</v>
       </c>
       <c r="E14">
-        <v>-381.876</v>
+        <v>-374.149</v>
       </c>
       <c r="F14">
-        <v>92.724</v>
+        <v>100.451</v>
       </c>
       <c r="G14">
         <v>43.4</v>
@@ -2429,28 +2429,28 @@
         <v>45.075</v>
       </c>
       <c r="M14">
-        <v>4.960734</v>
+        <v>5.3741285</v>
       </c>
       <c r="N14">
-        <v>40.11426599999999</v>
+        <v>39.7008715</v>
       </c>
       <c r="O14">
-        <v>5.014283249999999</v>
+        <v>4.9626089375</v>
       </c>
       <c r="P14">
-        <v>35.09998275</v>
+        <v>34.7382625625</v>
       </c>
       <c r="Q14">
-        <v>35.89998275</v>
+        <v>35.5382625625</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08248222969739369</v>
+        <v>0.08285677839901245</v>
       </c>
       <c r="T14">
-        <v>0.6185150911819033</v>
+        <v>0.6248305203759539</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.086356978624533</v>
+        <v>8.387406441807261</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07817102220714083</v>
+        <v>0.07814018228057522</v>
       </c>
       <c r="C15">
-        <v>761.783988354965</v>
+        <v>754.8378377234419</v>
       </c>
       <c r="D15">
-        <v>818.834988354965</v>
+        <v>819.6158377234419</v>
       </c>
       <c r="E15">
-        <v>-374.149</v>
+        <v>-366.422</v>
       </c>
       <c r="F15">
-        <v>100.451</v>
+        <v>108.178</v>
       </c>
       <c r="G15">
         <v>43.4</v>
@@ -2511,28 +2511,28 @@
         <v>45.075</v>
       </c>
       <c r="M15">
-        <v>5.3741285</v>
+        <v>5.787523</v>
       </c>
       <c r="N15">
-        <v>39.7008715</v>
+        <v>39.287477</v>
       </c>
       <c r="O15">
-        <v>4.9626089375</v>
+        <v>4.910934624999999</v>
       </c>
       <c r="P15">
-        <v>34.7382625625</v>
+        <v>34.376542375</v>
       </c>
       <c r="Q15">
-        <v>35.5382625625</v>
+        <v>35.176542375</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08285677839901245</v>
+        <v>0.08324003753555258</v>
       </c>
       <c r="T15">
-        <v>0.6248305203759539</v>
+        <v>0.6312928200163777</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.387406441807261</v>
+        <v>7.788305981678171</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07814018228057522</v>
+        <v>0.07821434235400961</v>
       </c>
       <c r="C16">
-        <v>754.8378377234419</v>
+        <v>745.2356563592875</v>
       </c>
       <c r="D16">
-        <v>819.6158377234419</v>
+        <v>817.7406563592876</v>
       </c>
       <c r="E16">
-        <v>-366.422</v>
+        <v>-358.695</v>
       </c>
       <c r="F16">
-        <v>108.178</v>
+        <v>115.905</v>
       </c>
       <c r="G16">
         <v>43.4</v>
@@ -2593,45 +2593,45 @@
         <v>45.075</v>
       </c>
       <c r="M16">
-        <v>5.787523</v>
+        <v>6.293641500000001</v>
       </c>
       <c r="N16">
-        <v>39.287477</v>
+        <v>38.7813585</v>
       </c>
       <c r="O16">
-        <v>4.910934624999999</v>
+        <v>4.8476698125</v>
       </c>
       <c r="P16">
-        <v>34.376542375</v>
+        <v>33.93368868749999</v>
       </c>
       <c r="Q16">
-        <v>35.176542375</v>
+        <v>34.7336886875</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08324003753555258</v>
+        <v>0.08363231453412895</v>
       </c>
       <c r="T16">
-        <v>0.6312928200163777</v>
+        <v>0.637907173765988</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.0468125</v>
+        <v>0.0475125</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.788305981678171</v>
+        <v>7.161990399357826</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07821434235400959</v>
+        <v>0.07819050242744396</v>
       </c>
       <c r="C17">
-        <v>745.235656359288</v>
+        <v>738.1105265291319</v>
       </c>
       <c r="D17">
-        <v>817.740656359288</v>
+        <v>818.3425265291319</v>
       </c>
       <c r="E17">
-        <v>-358.6950000000001</v>
+        <v>-350.968</v>
       </c>
       <c r="F17">
-        <v>115.905</v>
+        <v>123.632</v>
       </c>
       <c r="G17">
         <v>43.4</v>
@@ -2675,28 +2675,28 @@
         <v>45.075</v>
       </c>
       <c r="M17">
-        <v>6.293641500000001</v>
+        <v>6.7132176</v>
       </c>
       <c r="N17">
-        <v>38.7813585</v>
+        <v>38.3617824</v>
       </c>
       <c r="O17">
-        <v>4.8476698125</v>
+        <v>4.795222799999999</v>
       </c>
       <c r="P17">
-        <v>33.93368868749999</v>
+        <v>33.5665596</v>
       </c>
       <c r="Q17">
-        <v>34.7336886875</v>
+        <v>34.3665596</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08363231453412893</v>
+        <v>0.08403393146124283</v>
       </c>
       <c r="T17">
-        <v>0.6379071737659879</v>
+        <v>0.6446790121286843</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.161990399357827</v>
+        <v>6.714365999397963</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07819050242744396</v>
+        <v>0.07816666250087838</v>
       </c>
       <c r="C18">
-        <v>738.1105265291319</v>
+        <v>730.9862833236397</v>
       </c>
       <c r="D18">
-        <v>818.3425265291319</v>
+        <v>818.9452833236397</v>
       </c>
       <c r="E18">
-        <v>-350.968</v>
+        <v>-343.241</v>
       </c>
       <c r="F18">
-        <v>123.632</v>
+        <v>131.359</v>
       </c>
       <c r="G18">
         <v>43.4</v>
@@ -2757,28 +2757,28 @@
         <v>45.075</v>
       </c>
       <c r="M18">
-        <v>6.7132176</v>
+        <v>7.132793700000001</v>
       </c>
       <c r="N18">
-        <v>38.3617824</v>
+        <v>37.9422063</v>
       </c>
       <c r="O18">
-        <v>4.795222799999999</v>
+        <v>4.742775787499999</v>
       </c>
       <c r="P18">
-        <v>33.5665596</v>
+        <v>33.19943051249999</v>
       </c>
       <c r="Q18">
-        <v>34.3665596</v>
+        <v>33.9994305125</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08403393146124283</v>
+        <v>0.08444522590467274</v>
       </c>
       <c r="T18">
-        <v>0.6446790121286843</v>
+        <v>0.6516140273193973</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.714365999397963</v>
+        <v>6.319403293551024</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07816666250087838</v>
+        <v>0.07830032257431274</v>
       </c>
       <c r="C19">
-        <v>730.9862833236397</v>
+        <v>719.8913079302424</v>
       </c>
       <c r="D19">
-        <v>818.9452833236397</v>
+        <v>815.5773079302425</v>
       </c>
       <c r="E19">
-        <v>-343.241</v>
+        <v>-335.514</v>
       </c>
       <c r="F19">
-        <v>131.359</v>
+        <v>139.086</v>
       </c>
       <c r="G19">
         <v>43.4</v>
@@ -2839,45 +2839,45 @@
         <v>45.075</v>
       </c>
       <c r="M19">
-        <v>7.132793700000001</v>
+        <v>7.691455800000001</v>
       </c>
       <c r="N19">
-        <v>37.9422063</v>
+        <v>37.3835442</v>
       </c>
       <c r="O19">
-        <v>4.742775787499999</v>
+        <v>4.672943024999999</v>
       </c>
       <c r="P19">
-        <v>33.19943051249999</v>
+        <v>32.71060117499999</v>
       </c>
       <c r="Q19">
-        <v>33.9994305125</v>
+        <v>33.510601175</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08444522590467274</v>
+        <v>0.08486655191989359</v>
       </c>
       <c r="T19">
-        <v>0.6516140273193973</v>
+        <v>0.6587181892220789</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.0475125</v>
+        <v>0.0483875</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.319403293551024</v>
+        <v>5.860399015749397</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07830032257431276</v>
+        <v>0.07828523264774713</v>
       </c>
       <c r="C20">
-        <v>719.8913079302421</v>
+        <v>712.5431570466608</v>
       </c>
       <c r="D20">
-        <v>815.5773079302421</v>
+        <v>815.9561570466608</v>
       </c>
       <c r="E20">
-        <v>-335.514</v>
+        <v>-327.787</v>
       </c>
       <c r="F20">
-        <v>139.086</v>
+        <v>146.813</v>
       </c>
       <c r="G20">
         <v>43.4</v>
@@ -2921,28 +2921,28 @@
         <v>45.075</v>
       </c>
       <c r="M20">
-        <v>7.691455800000001</v>
+        <v>8.118758900000001</v>
       </c>
       <c r="N20">
-        <v>37.3835442</v>
+        <v>36.95624109999999</v>
       </c>
       <c r="O20">
-        <v>4.672943024999999</v>
+        <v>4.619530137499999</v>
       </c>
       <c r="P20">
-        <v>32.71060117499999</v>
+        <v>32.33671096249999</v>
       </c>
       <c r="Q20">
-        <v>33.510601175</v>
+        <v>33.1367109625</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08486655191989359</v>
+        <v>0.08529828104660139</v>
       </c>
       <c r="T20">
-        <v>0.6587181892220789</v>
+        <v>0.6659977625297651</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.860399015749397</v>
+        <v>5.551956962288902</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07828523264774713</v>
+        <v>0.07827014272118152</v>
       </c>
       <c r="C21">
-        <v>712.5431570466608</v>
+        <v>705.1953582899791</v>
       </c>
       <c r="D21">
-        <v>815.9561570466608</v>
+        <v>816.3353582899791</v>
       </c>
       <c r="E21">
-        <v>-327.787</v>
+        <v>-320.06</v>
       </c>
       <c r="F21">
-        <v>146.813</v>
+        <v>154.54</v>
       </c>
       <c r="G21">
         <v>43.4</v>
@@ -3003,28 +3003,28 @@
         <v>45.075</v>
       </c>
       <c r="M21">
-        <v>8.118758900000001</v>
+        <v>8.546062000000001</v>
       </c>
       <c r="N21">
-        <v>36.95624109999999</v>
+        <v>36.528938</v>
       </c>
       <c r="O21">
-        <v>4.619530137499999</v>
+        <v>4.56611725</v>
       </c>
       <c r="P21">
-        <v>32.33671096249999</v>
+        <v>31.96282075</v>
       </c>
       <c r="Q21">
-        <v>33.1367109625</v>
+        <v>32.76282075</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08529828104660139</v>
+        <v>0.08574080340147688</v>
       </c>
       <c r="T21">
-        <v>0.6659977625297651</v>
+        <v>0.6734593251701434</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.551956962288902</v>
+        <v>5.274359114174458</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07827014272118152</v>
+        <v>0.07825505279461589</v>
       </c>
       <c r="C22">
-        <v>705.1953582899791</v>
+        <v>697.84791215136</v>
       </c>
       <c r="D22">
-        <v>816.3353582899791</v>
+        <v>816.7149121513601</v>
       </c>
       <c r="E22">
-        <v>-320.06</v>
+        <v>-312.333</v>
       </c>
       <c r="F22">
-        <v>154.54</v>
+        <v>162.267</v>
       </c>
       <c r="G22">
         <v>43.4</v>
@@ -3085,28 +3085,28 @@
         <v>45.075</v>
       </c>
       <c r="M22">
-        <v>8.546062000000001</v>
+        <v>8.973365100000002</v>
       </c>
       <c r="N22">
-        <v>36.528938</v>
+        <v>36.10163489999999</v>
       </c>
       <c r="O22">
-        <v>4.56611725</v>
+        <v>4.512704362499999</v>
       </c>
       <c r="P22">
-        <v>31.96282075</v>
+        <v>31.58893053749999</v>
       </c>
       <c r="Q22">
-        <v>32.76282075</v>
+        <v>32.3889305375</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08574080340147688</v>
+        <v>0.08619452885394417</v>
       </c>
       <c r="T22">
-        <v>0.6734593251701434</v>
+        <v>0.6811097881305312</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.274359114174458</v>
+        <v>5.023199156356625</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07825505279461589</v>
+        <v>0.07823996286805027</v>
       </c>
       <c r="C23">
-        <v>697.8479121513601</v>
+        <v>690.5008191228798</v>
       </c>
       <c r="D23">
-        <v>816.7149121513601</v>
+        <v>817.0948191228798</v>
       </c>
       <c r="E23">
-        <v>-312.333</v>
+        <v>-304.606</v>
       </c>
       <c r="F23">
-        <v>162.267</v>
+        <v>169.994</v>
       </c>
       <c r="G23">
         <v>43.4</v>
@@ -3167,28 +3167,28 @@
         <v>45.075</v>
       </c>
       <c r="M23">
-        <v>8.973365100000001</v>
+        <v>9.4006682</v>
       </c>
       <c r="N23">
-        <v>36.10163489999999</v>
+        <v>35.6743318</v>
       </c>
       <c r="O23">
-        <v>4.512704362499999</v>
+        <v>4.459291475</v>
       </c>
       <c r="P23">
-        <v>31.58893053749999</v>
+        <v>31.215040325</v>
       </c>
       <c r="Q23">
-        <v>32.3889305375</v>
+        <v>32.015040325</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08619452885394416</v>
+        <v>0.08665988829237214</v>
       </c>
       <c r="T23">
-        <v>0.6811097881305311</v>
+        <v>0.6889564168078521</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.023199156356626</v>
+        <v>4.79487192197678</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07823996286805027</v>
+        <v>0.07822487294148465</v>
       </c>
       <c r="C24">
-        <v>690.5008191228798</v>
+        <v>683.1540796975305</v>
       </c>
       <c r="D24">
-        <v>817.0948191228798</v>
+        <v>817.4750796975305</v>
       </c>
       <c r="E24">
-        <v>-304.606</v>
+        <v>-296.879</v>
       </c>
       <c r="F24">
-        <v>169.994</v>
+        <v>177.721</v>
       </c>
       <c r="G24">
         <v>43.4</v>
@@ -3249,28 +3249,28 @@
         <v>45.075</v>
       </c>
       <c r="M24">
-        <v>9.4006682</v>
+        <v>9.827971300000002</v>
       </c>
       <c r="N24">
-        <v>35.6743318</v>
+        <v>35.24702869999999</v>
       </c>
       <c r="O24">
-        <v>4.459291475</v>
+        <v>4.405878587499999</v>
       </c>
       <c r="P24">
-        <v>31.215040325</v>
+        <v>30.8411501125</v>
       </c>
       <c r="Q24">
-        <v>32.015040325</v>
+        <v>31.6411501125</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08665988829237214</v>
+        <v>0.08713733498894111</v>
       </c>
       <c r="T24">
-        <v>0.6889564168078521</v>
+        <v>0.6970068540222462</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.79487192197678</v>
+        <v>4.586399229716919</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07822487294148465</v>
+        <v>0.07873478301491904</v>
       </c>
       <c r="C25">
-        <v>683.1540796975305</v>
+        <v>662.7705889069118</v>
       </c>
       <c r="D25">
-        <v>817.4750796975305</v>
+        <v>804.8185889069119</v>
       </c>
       <c r="E25">
-        <v>-296.879</v>
+        <v>-289.152</v>
       </c>
       <c r="F25">
-        <v>177.721</v>
+        <v>185.448</v>
       </c>
       <c r="G25">
         <v>43.4</v>
@@ -3331,45 +3331,45 @@
         <v>45.075</v>
       </c>
       <c r="M25">
-        <v>9.827971300000002</v>
+        <v>10.7188944</v>
       </c>
       <c r="N25">
-        <v>35.24702869999999</v>
+        <v>34.35610559999999</v>
       </c>
       <c r="O25">
-        <v>4.405878587499999</v>
+        <v>4.294513199999999</v>
       </c>
       <c r="P25">
-        <v>30.8411501125</v>
+        <v>30.06159239999999</v>
       </c>
       <c r="Q25">
-        <v>31.6411501125</v>
+        <v>30.8615924</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08713733498894111</v>
+        <v>0.0876273460722619</v>
       </c>
       <c r="T25">
-        <v>0.6970068540222462</v>
+        <v>0.7052691448475455</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.0483875</v>
+        <v>0.050575</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.586399229716919</v>
+        <v>4.205191162252702</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07873478301491903</v>
+        <v>0.07874156808835341</v>
       </c>
       <c r="C26">
-        <v>662.7705889069122</v>
+        <v>654.87781801184</v>
       </c>
       <c r="D26">
-        <v>804.8185889069122</v>
+        <v>804.6528180118401</v>
       </c>
       <c r="E26">
-        <v>-289.152</v>
+        <v>-281.425</v>
       </c>
       <c r="F26">
-        <v>185.448</v>
+        <v>193.175</v>
       </c>
       <c r="G26">
         <v>43.4</v>
@@ -3413,28 +3413,28 @@
         <v>45.075</v>
       </c>
       <c r="M26">
-        <v>10.7188944</v>
+        <v>11.165515</v>
       </c>
       <c r="N26">
-        <v>34.35610559999999</v>
+        <v>33.909485</v>
       </c>
       <c r="O26">
-        <v>4.294513199999999</v>
+        <v>4.238685625</v>
       </c>
       <c r="P26">
-        <v>30.06159239999999</v>
+        <v>29.670799375</v>
       </c>
       <c r="Q26">
-        <v>30.8615924</v>
+        <v>30.470799375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08762734607226189</v>
+        <v>0.08813042411780456</v>
       </c>
       <c r="T26">
-        <v>0.7052691448475454</v>
+        <v>0.713751763428186</v>
       </c>
       <c r="U26">
         <v>0.0578</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.205191162252703</v>
+        <v>4.036983515762595</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07874156808835341</v>
+        <v>0.0795446031617878</v>
       </c>
       <c r="C27">
-        <v>654.87781801184</v>
+        <v>628.002143134755</v>
       </c>
       <c r="D27">
-        <v>804.6528180118401</v>
+        <v>785.5041431347551</v>
       </c>
       <c r="E27">
-        <v>-281.425</v>
+        <v>-273.698</v>
       </c>
       <c r="F27">
-        <v>193.175</v>
+        <v>200.902</v>
       </c>
       <c r="G27">
         <v>43.4</v>
@@ -3495,45 +3495,45 @@
         <v>45.075</v>
       </c>
       <c r="M27">
-        <v>11.165515</v>
+        <v>12.3152926</v>
       </c>
       <c r="N27">
-        <v>33.909485</v>
+        <v>32.7597074</v>
       </c>
       <c r="O27">
-        <v>4.238685625</v>
+        <v>4.094963425</v>
       </c>
       <c r="P27">
-        <v>29.670799375</v>
+        <v>28.664743975</v>
       </c>
       <c r="Q27">
-        <v>30.470799375</v>
+        <v>29.464743975</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08813042411780456</v>
+        <v>0.08864709886728082</v>
       </c>
       <c r="T27">
-        <v>0.713751763428186</v>
+        <v>0.7224636419704656</v>
       </c>
       <c r="U27">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.050575</v>
+        <v>0.0536375</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.036983515762595</v>
+        <v>3.660083561473805</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0795446031617878</v>
+        <v>0.07958201323522218</v>
       </c>
       <c r="C28">
-        <v>628.002143134755</v>
+        <v>619.4052788234403</v>
       </c>
       <c r="D28">
-        <v>785.5041431347551</v>
+        <v>784.6342788234404</v>
       </c>
       <c r="E28">
-        <v>-273.698</v>
+        <v>-265.971</v>
       </c>
       <c r="F28">
-        <v>200.902</v>
+        <v>208.629</v>
       </c>
       <c r="G28">
         <v>43.4</v>
@@ -3577,28 +3577,28 @@
         <v>45.075</v>
       </c>
       <c r="M28">
-        <v>12.3152926</v>
+        <v>12.7889577</v>
       </c>
       <c r="N28">
-        <v>32.7597074</v>
+        <v>32.28604229999999</v>
       </c>
       <c r="O28">
-        <v>4.094963425</v>
+        <v>4.035755287499999</v>
       </c>
       <c r="P28">
-        <v>28.664743975</v>
+        <v>28.25028701249999</v>
       </c>
       <c r="Q28">
-        <v>29.464743975</v>
+        <v>29.0502870125</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08864709886728082</v>
+        <v>0.08917792908934546</v>
       </c>
       <c r="T28">
-        <v>0.7224636419704656</v>
+        <v>0.7314142021166433</v>
       </c>
       <c r="U28">
         <v>0.0613</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.660083561473805</v>
+        <v>3.524524911048849</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07958201323522218</v>
+        <v>0.08030542330865659</v>
       </c>
       <c r="C29">
-        <v>619.4052788234403</v>
+        <v>595.2283330805512</v>
       </c>
       <c r="D29">
-        <v>784.6342788234404</v>
+        <v>768.1843330805513</v>
       </c>
       <c r="E29">
-        <v>-265.971</v>
+        <v>-258.244</v>
       </c>
       <c r="F29">
-        <v>208.629</v>
+        <v>216.356</v>
       </c>
       <c r="G29">
         <v>43.4</v>
@@ -3659,45 +3659,45 @@
         <v>45.075</v>
       </c>
       <c r="M29">
-        <v>12.7889577</v>
+        <v>13.8684196</v>
       </c>
       <c r="N29">
-        <v>32.28604229999999</v>
+        <v>31.20658039999999</v>
       </c>
       <c r="O29">
-        <v>4.035755287499999</v>
+        <v>3.900822549999999</v>
       </c>
       <c r="P29">
-        <v>28.25028701249999</v>
+        <v>27.30575784999999</v>
       </c>
       <c r="Q29">
-        <v>29.0502870125</v>
+        <v>28.10575785</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08917792908934546</v>
+        <v>0.08972350459535636</v>
       </c>
       <c r="T29">
-        <v>0.7314142021166433</v>
+        <v>0.740613388933548</v>
       </c>
       <c r="U29">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.0536375</v>
+        <v>0.05608750000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.524524911048849</v>
+        <v>3.250190093758051</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08030542330865659</v>
+        <v>0.08036733338209096</v>
       </c>
       <c r="C30">
-        <v>595.2283330805512</v>
+        <v>586.1255153989714</v>
       </c>
       <c r="D30">
-        <v>768.1843330805513</v>
+        <v>766.8085153989715</v>
       </c>
       <c r="E30">
-        <v>-258.244</v>
+        <v>-250.517</v>
       </c>
       <c r="F30">
-        <v>216.356</v>
+        <v>224.083</v>
       </c>
       <c r="G30">
         <v>43.4</v>
@@ -3741,28 +3741,28 @@
         <v>45.075</v>
       </c>
       <c r="M30">
-        <v>13.8684196</v>
+        <v>14.3637203</v>
       </c>
       <c r="N30">
-        <v>31.20658039999999</v>
+        <v>30.71127969999999</v>
       </c>
       <c r="O30">
-        <v>3.900822549999999</v>
+        <v>3.838909962499999</v>
       </c>
       <c r="P30">
-        <v>27.30575784999999</v>
+        <v>26.87236973749999</v>
       </c>
       <c r="Q30">
-        <v>28.10575785</v>
+        <v>27.6723697375</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08972350459535636</v>
+        <v>0.09028444842548022</v>
       </c>
       <c r="T30">
-        <v>0.740613388933548</v>
+        <v>0.7500717077734642</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.250190093758051</v>
+        <v>3.138114573283635</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08036733338209096</v>
+        <v>0.08042924345552534</v>
       </c>
       <c r="C31">
-        <v>586.1255153989715</v>
+        <v>577.0276170840996</v>
       </c>
       <c r="D31">
-        <v>766.8085153989715</v>
+        <v>765.4376170840997</v>
       </c>
       <c r="E31">
-        <v>-250.517</v>
+        <v>-242.79</v>
       </c>
       <c r="F31">
-        <v>224.083</v>
+        <v>231.81</v>
       </c>
       <c r="G31">
         <v>43.4</v>
@@ -3823,28 +3823,28 @@
         <v>45.075</v>
       </c>
       <c r="M31">
-        <v>14.3637203</v>
+        <v>14.859021</v>
       </c>
       <c r="N31">
-        <v>30.7112797</v>
+        <v>30.215979</v>
       </c>
       <c r="O31">
-        <v>3.838909962499999</v>
+        <v>3.776997375</v>
       </c>
       <c r="P31">
-        <v>26.87236973749999</v>
+        <v>26.438981625</v>
       </c>
       <c r="Q31">
-        <v>27.6723697375</v>
+        <v>27.238981625</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09028444842548022</v>
+        <v>0.09086141922217905</v>
       </c>
       <c r="T31">
-        <v>0.7500717077734641</v>
+        <v>0.7598002642945207</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.138114573283636</v>
+        <v>3.033510754174181</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08042924345552534</v>
+        <v>0.08260690352895972</v>
       </c>
       <c r="C32">
-        <v>577.0276170840996</v>
+        <v>524.0139241647317</v>
       </c>
       <c r="D32">
-        <v>765.4376170840997</v>
+        <v>720.1509241647318</v>
       </c>
       <c r="E32">
-        <v>-242.79</v>
+        <v>-235.063</v>
       </c>
       <c r="F32">
-        <v>231.81</v>
+        <v>239.537</v>
       </c>
       <c r="G32">
         <v>43.4</v>
@@ -3905,45 +3905,45 @@
         <v>45.075</v>
       </c>
       <c r="M32">
-        <v>14.859021</v>
+        <v>17.2227103</v>
       </c>
       <c r="N32">
-        <v>30.215979</v>
+        <v>27.85228969999999</v>
       </c>
       <c r="O32">
-        <v>3.776997375</v>
+        <v>3.481536212499999</v>
       </c>
       <c r="P32">
-        <v>26.438981625</v>
+        <v>24.37075348749999</v>
       </c>
       <c r="Q32">
-        <v>27.238981625</v>
+        <v>25.1707534875</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09086141922217905</v>
+        <v>0.09145511381008656</v>
       </c>
       <c r="T32">
-        <v>0.7598002642945207</v>
+        <v>0.7698108079611152</v>
       </c>
       <c r="U32">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V32">
         <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.05608750000000001</v>
+        <v>0.06291250000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.033510754174181</v>
+        <v>2.617183893524586</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08260690352895972</v>
+        <v>0.08273706360239411</v>
       </c>
       <c r="C33">
-        <v>524.0139241647317</v>
+        <v>513.749231992389</v>
       </c>
       <c r="D33">
-        <v>720.1509241647318</v>
+        <v>717.613231992389</v>
       </c>
       <c r="E33">
-        <v>-235.063</v>
+        <v>-227.336</v>
       </c>
       <c r="F33">
-        <v>239.537</v>
+        <v>247.264</v>
       </c>
       <c r="G33">
         <v>43.4</v>
@@ -3987,28 +3987,28 @@
         <v>45.075</v>
       </c>
       <c r="M33">
-        <v>17.2227103</v>
+        <v>17.7782816</v>
       </c>
       <c r="N33">
-        <v>27.85228969999999</v>
+        <v>27.29671839999999</v>
       </c>
       <c r="O33">
-        <v>3.481536212499999</v>
+        <v>3.412089799999999</v>
       </c>
       <c r="P33">
-        <v>24.37075348749999</v>
+        <v>23.88462859999999</v>
       </c>
       <c r="Q33">
-        <v>25.1707534875</v>
+        <v>24.6846286</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09145511381008656</v>
+        <v>0.09206627000352074</v>
       </c>
       <c r="T33">
-        <v>0.7698108079611152</v>
+        <v>0.7801157793826096</v>
       </c>
       <c r="U33">
         <v>0.07190000000000001</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.617183893524586</v>
+        <v>2.535396896851942</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08273706360239411</v>
+        <v>0.08399334867582847</v>
       </c>
       <c r="C34">
-        <v>513.749231992389</v>
+        <v>482.4179442536293</v>
       </c>
       <c r="D34">
-        <v>717.613231992389</v>
+        <v>694.0089442536294</v>
       </c>
       <c r="E34">
-        <v>-227.336</v>
+        <v>-219.609</v>
       </c>
       <c r="F34">
-        <v>247.264</v>
+        <v>254.991</v>
       </c>
       <c r="G34">
         <v>43.4</v>
@@ -4069,45 +4069,45 @@
         <v>45.075</v>
       </c>
       <c r="M34">
-        <v>17.7782816</v>
+        <v>19.3283178</v>
       </c>
       <c r="N34">
-        <v>27.29671839999999</v>
+        <v>25.74668219999999</v>
       </c>
       <c r="O34">
-        <v>3.412089799999999</v>
+        <v>3.218335274999999</v>
       </c>
       <c r="P34">
-        <v>23.88462859999999</v>
+        <v>22.52834692499999</v>
       </c>
       <c r="Q34">
-        <v>24.6846286</v>
+        <v>23.328346925</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09206627000352074</v>
+        <v>0.09269566966541565</v>
       </c>
       <c r="T34">
-        <v>0.7801157793826096</v>
+        <v>0.7907283618913127</v>
       </c>
       <c r="U34">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V34">
         <v>0.125</v>
       </c>
       <c r="W34">
-        <v>0.06291250000000001</v>
+        <v>0.06632500000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.535396896851942</v>
+        <v>2.33207051262371</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08399334867582847</v>
+        <v>0.08415763374926287</v>
       </c>
       <c r="C35">
-        <v>482.4179442536293</v>
+        <v>471.7185161024004</v>
       </c>
       <c r="D35">
-        <v>694.0089442536294</v>
+        <v>691.0365161024005</v>
       </c>
       <c r="E35">
-        <v>-219.609</v>
+        <v>-211.882</v>
       </c>
       <c r="F35">
-        <v>254.991</v>
+        <v>262.718</v>
       </c>
       <c r="G35">
         <v>43.4</v>
@@ -4151,28 +4151,28 @@
         <v>45.075</v>
       </c>
       <c r="M35">
-        <v>19.3283178</v>
+        <v>19.9140244</v>
       </c>
       <c r="N35">
-        <v>25.74668219999999</v>
+        <v>25.16097559999999</v>
       </c>
       <c r="O35">
-        <v>3.218335274999999</v>
+        <v>3.145121949999999</v>
       </c>
       <c r="P35">
-        <v>22.52834692499999</v>
+        <v>22.01585364999999</v>
       </c>
       <c r="Q35">
-        <v>23.328346925</v>
+        <v>22.81585365</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09269566966541565</v>
+        <v>0.09334414204433769</v>
       </c>
       <c r="T35">
-        <v>0.7907283618913127</v>
+        <v>0.8016625378093705</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.33207051262371</v>
+        <v>2.263480203428895</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08415763374926287</v>
+        <v>0.08432191882269724</v>
       </c>
       <c r="C36">
-        <v>471.7185161024004</v>
+        <v>461.0444410795741</v>
       </c>
       <c r="D36">
-        <v>691.0365161024005</v>
+        <v>688.0894410795742</v>
       </c>
       <c r="E36">
-        <v>-211.882</v>
+        <v>-204.155</v>
       </c>
       <c r="F36">
-        <v>262.718</v>
+        <v>270.4450000000001</v>
       </c>
       <c r="G36">
         <v>43.4</v>
@@ -4233,28 +4233,28 @@
         <v>45.075</v>
       </c>
       <c r="M36">
-        <v>19.9140244</v>
+        <v>20.499731</v>
       </c>
       <c r="N36">
-        <v>25.16097559999999</v>
+        <v>24.57526899999999</v>
       </c>
       <c r="O36">
-        <v>3.145121949999999</v>
+        <v>3.071908624999999</v>
       </c>
       <c r="P36">
-        <v>22.01585364999999</v>
+        <v>21.50336037499999</v>
       </c>
       <c r="Q36">
-        <v>22.81585365</v>
+        <v>22.303360375</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09334414204433769</v>
+        <v>0.09401256741953423</v>
       </c>
       <c r="T36">
-        <v>0.8016625378093705</v>
+        <v>0.8129331499095223</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.263480203428895</v>
+        <v>2.198809340473784</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08432191882269724</v>
+        <v>0.08448620389613164</v>
       </c>
       <c r="C37">
-        <v>461.0444410795741</v>
+        <v>450.3953961908924</v>
       </c>
       <c r="D37">
-        <v>688.0894410795742</v>
+        <v>685.1673961908924</v>
       </c>
       <c r="E37">
-        <v>-204.155</v>
+        <v>-196.428</v>
       </c>
       <c r="F37">
-        <v>270.4450000000001</v>
+        <v>278.172</v>
       </c>
       <c r="G37">
         <v>43.4</v>
@@ -4315,28 +4315,28 @@
         <v>45.075</v>
       </c>
       <c r="M37">
-        <v>20.499731</v>
+        <v>21.0854376</v>
       </c>
       <c r="N37">
-        <v>24.57526899999999</v>
+        <v>23.98956239999999</v>
       </c>
       <c r="O37">
-        <v>3.071908624999999</v>
+        <v>2.998695299999999</v>
       </c>
       <c r="P37">
-        <v>21.50336037499999</v>
+        <v>20.9908671</v>
       </c>
       <c r="Q37">
-        <v>22.303360375</v>
+        <v>21.7908671</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09401256741953423</v>
+        <v>0.09470188108770569</v>
       </c>
       <c r="T37">
-        <v>0.8129331499095223</v>
+        <v>0.8245559686378038</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.198809340473784</v>
+        <v>2.137731303238401</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08448620389613165</v>
+        <v>0.08465048896956602</v>
       </c>
       <c r="C38">
-        <v>450.3953961908921</v>
+        <v>439.7710639054161</v>
       </c>
       <c r="D38">
-        <v>685.1673961908922</v>
+        <v>682.2700639054161</v>
       </c>
       <c r="E38">
-        <v>-196.428</v>
+        <v>-188.701</v>
       </c>
       <c r="F38">
-        <v>278.172</v>
+        <v>285.899</v>
       </c>
       <c r="G38">
         <v>43.4</v>
@@ -4397,28 +4397,28 @@
         <v>45.075</v>
       </c>
       <c r="M38">
-        <v>21.0854376</v>
+        <v>21.6711442</v>
       </c>
       <c r="N38">
-        <v>23.98956239999999</v>
+        <v>23.4038558</v>
       </c>
       <c r="O38">
-        <v>2.998695299999999</v>
+        <v>2.925481974999999</v>
       </c>
       <c r="P38">
-        <v>20.9908671</v>
+        <v>20.47837382499999</v>
       </c>
       <c r="Q38">
-        <v>21.7908671</v>
+        <v>21.278373825</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09470188108770569</v>
+        <v>0.09541307772946987</v>
       </c>
       <c r="T38">
-        <v>0.8245559686378038</v>
+        <v>0.8365477657384117</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.137731303238401</v>
+        <v>2.079954781529255</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08465048896956602</v>
+        <v>0.0848147740430004</v>
       </c>
       <c r="C39">
-        <v>439.7710639054161</v>
+        <v>429.1711320404962</v>
       </c>
       <c r="D39">
-        <v>682.2700639054161</v>
+        <v>679.3971320404962</v>
       </c>
       <c r="E39">
-        <v>-188.701</v>
+        <v>-180.974</v>
       </c>
       <c r="F39">
-        <v>285.899</v>
+        <v>293.626</v>
       </c>
       <c r="G39">
         <v>43.4</v>
@@ -4479,28 +4479,28 @@
         <v>45.075</v>
       </c>
       <c r="M39">
-        <v>21.6711442</v>
+        <v>22.25685080000001</v>
       </c>
       <c r="N39">
-        <v>23.4038558</v>
+        <v>22.81814919999999</v>
       </c>
       <c r="O39">
-        <v>2.925481974999999</v>
+        <v>2.852268649999999</v>
       </c>
       <c r="P39">
-        <v>20.47837382499999</v>
+        <v>19.96588054999999</v>
       </c>
       <c r="Q39">
-        <v>21.278373825</v>
+        <v>20.76588054999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09541307772946987</v>
+        <v>0.09614721619838774</v>
       </c>
       <c r="T39">
-        <v>0.8365477657384117</v>
+        <v>0.8489263950035554</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.079954781529255</v>
+        <v>2.025219129383748</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0848147740430004</v>
+        <v>0.08982480911643478</v>
       </c>
       <c r="C40">
-        <v>429.1711320404962</v>
+        <v>344.128556376979</v>
       </c>
       <c r="D40">
-        <v>679.3971320404962</v>
+        <v>602.0815563769791</v>
       </c>
       <c r="E40">
-        <v>-180.974</v>
+        <v>-173.247</v>
       </c>
       <c r="F40">
-        <v>293.626</v>
+        <v>301.353</v>
       </c>
       <c r="G40">
         <v>43.4</v>
@@ -4561,45 +4561,45 @@
         <v>45.075</v>
       </c>
       <c r="M40">
-        <v>22.25685080000001</v>
+        <v>27.12177</v>
       </c>
       <c r="N40">
-        <v>22.81814919999999</v>
+        <v>17.95322999999999</v>
       </c>
       <c r="O40">
-        <v>2.852268649999999</v>
+        <v>2.244153749999999</v>
       </c>
       <c r="P40">
-        <v>19.96588054999999</v>
+        <v>15.70907625</v>
       </c>
       <c r="Q40">
-        <v>20.76588054999999</v>
+        <v>16.50907625</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09614721619838774</v>
+        <v>0.09690542478104062</v>
       </c>
       <c r="T40">
-        <v>0.8489263950035554</v>
+        <v>0.8617108809659169</v>
       </c>
       <c r="U40">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V40">
         <v>0.125</v>
       </c>
       <c r="W40">
-        <v>0.06632500000000001</v>
+        <v>0.07875</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.025219129383748</v>
+        <v>1.661949054209957</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08982480911643478</v>
+        <v>0.09011334418986916</v>
       </c>
       <c r="C41">
-        <v>344.128556376979</v>
+        <v>332.481255409885</v>
       </c>
       <c r="D41">
-        <v>602.0815563769791</v>
+        <v>598.161255409885</v>
       </c>
       <c r="E41">
-        <v>-173.247</v>
+        <v>-165.52</v>
       </c>
       <c r="F41">
-        <v>301.353</v>
+        <v>309.08</v>
       </c>
       <c r="G41">
         <v>43.4</v>
@@ -4643,28 +4643,28 @@
         <v>45.075</v>
       </c>
       <c r="M41">
-        <v>27.12177</v>
+        <v>27.8172</v>
       </c>
       <c r="N41">
-        <v>17.95322999999999</v>
+        <v>17.25779999999999</v>
       </c>
       <c r="O41">
-        <v>2.244153749999999</v>
+        <v>2.157224999999999</v>
       </c>
       <c r="P41">
-        <v>15.70907625</v>
+        <v>15.10057499999999</v>
       </c>
       <c r="Q41">
-        <v>16.50907625</v>
+        <v>15.900575</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09690542478104062</v>
+        <v>0.09768890698311528</v>
       </c>
       <c r="T41">
-        <v>0.8617108809659169</v>
+        <v>0.8749215164603573</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.661949054209957</v>
+        <v>1.620400327854708</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09011334418986916</v>
+        <v>0.09040187926330355</v>
       </c>
       <c r="C42">
-        <v>332.481255409885</v>
+        <v>320.8846762664497</v>
       </c>
       <c r="D42">
-        <v>598.161255409885</v>
+        <v>594.2916762664497</v>
       </c>
       <c r="E42">
-        <v>-165.52</v>
+        <v>-157.793</v>
       </c>
       <c r="F42">
-        <v>309.08</v>
+        <v>316.807</v>
       </c>
       <c r="G42">
         <v>43.4</v>
@@ -4725,28 +4725,28 @@
         <v>45.075</v>
       </c>
       <c r="M42">
-        <v>27.8172</v>
+        <v>28.51263</v>
       </c>
       <c r="N42">
-        <v>17.25779999999999</v>
+        <v>16.56236999999999</v>
       </c>
       <c r="O42">
-        <v>2.157224999999999</v>
+        <v>2.070296249999999</v>
       </c>
       <c r="P42">
-        <v>15.10057499999999</v>
+        <v>14.49207375</v>
       </c>
       <c r="Q42">
-        <v>15.900575</v>
+        <v>15.29207375</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09768890698311528</v>
+        <v>0.09849894790390432</v>
       </c>
       <c r="T42">
-        <v>0.8749215164603573</v>
+        <v>0.8885799701071514</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.620400327854708</v>
+        <v>1.58087836863874</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09040187926330355</v>
+        <v>0.09069041433673793</v>
       </c>
       <c r="C43">
-        <v>320.8846762664497</v>
+        <v>309.3378408965487</v>
       </c>
       <c r="D43">
-        <v>594.2916762664497</v>
+        <v>590.4718408965488</v>
       </c>
       <c r="E43">
-        <v>-157.793</v>
+        <v>-150.066</v>
       </c>
       <c r="F43">
-        <v>316.807</v>
+        <v>324.534</v>
       </c>
       <c r="G43">
         <v>43.4</v>
@@ -4807,28 +4807,28 @@
         <v>45.075</v>
       </c>
       <c r="M43">
-        <v>28.51263</v>
+        <v>29.20806</v>
       </c>
       <c r="N43">
-        <v>16.56236999999999</v>
+        <v>15.86693999999999</v>
       </c>
       <c r="O43">
-        <v>2.070296249999999</v>
+        <v>1.983367499999999</v>
       </c>
       <c r="P43">
-        <v>14.49207375</v>
+        <v>13.88357249999999</v>
       </c>
       <c r="Q43">
-        <v>15.29207375</v>
+        <v>14.6835725</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09849894790390432</v>
+        <v>0.09933692127023781</v>
       </c>
       <c r="T43">
-        <v>0.8885799701071514</v>
+        <v>0.9027094049141798</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.58087836863874</v>
+        <v>1.543238407480675</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09069041433673794</v>
+        <v>0.09097894941017232</v>
       </c>
       <c r="C44">
-        <v>309.3378408965486</v>
+        <v>297.8397962353008</v>
       </c>
       <c r="D44">
-        <v>590.4718408965487</v>
+        <v>586.7007962353008</v>
       </c>
       <c r="E44">
-        <v>-150.066</v>
+        <v>-142.339</v>
       </c>
       <c r="F44">
-        <v>324.534</v>
+        <v>332.261</v>
       </c>
       <c r="G44">
         <v>43.4</v>
@@ -4889,28 +4889,28 @@
         <v>45.075</v>
       </c>
       <c r="M44">
-        <v>29.20806</v>
+        <v>29.90349</v>
       </c>
       <c r="N44">
-        <v>15.86694</v>
+        <v>15.17150999999999</v>
       </c>
       <c r="O44">
-        <v>1.9833675</v>
+        <v>1.896438749999999</v>
       </c>
       <c r="P44">
-        <v>13.8835725</v>
+        <v>13.27507124999999</v>
       </c>
       <c r="Q44">
-        <v>14.6835725</v>
+        <v>14.07507125</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0993369212702378</v>
+        <v>0.1002042972108286</v>
       </c>
       <c r="T44">
-        <v>0.9027094049141797</v>
+        <v>0.91733460936356</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.543238407480675</v>
+        <v>1.507349142190426</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09097894941017232</v>
+        <v>0.1140923026547029</v>
       </c>
       <c r="C45">
-        <v>297.8397962353008</v>
+        <v>91.54542882936323</v>
       </c>
       <c r="D45">
-        <v>586.7007962353008</v>
+        <v>388.1334288293633</v>
       </c>
       <c r="E45">
-        <v>-142.339</v>
+        <v>-134.612</v>
       </c>
       <c r="F45">
-        <v>332.261</v>
+        <v>339.988</v>
       </c>
       <c r="G45">
         <v>43.4</v>
@@ -4971,45 +4971,45 @@
         <v>45.075</v>
       </c>
       <c r="M45">
-        <v>29.90349</v>
+        <v>49.9102384</v>
       </c>
       <c r="N45">
-        <v>15.17150999999999</v>
+        <v>-4.835238400000009</v>
       </c>
       <c r="O45">
-        <v>1.896438749999999</v>
+        <v>-0.6044048000000011</v>
       </c>
       <c r="P45">
-        <v>13.27507124999999</v>
+        <v>-4.230833600000008</v>
       </c>
       <c r="Q45">
-        <v>14.07507125</v>
+        <v>-3.430833600000003</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1002042972108286</v>
+        <v>0.1014144716608019</v>
       </c>
       <c r="T45">
-        <v>0.91733460936356</v>
+        <v>0.9377398891528755</v>
       </c>
       <c r="U45">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.125</v>
+        <v>0.1128901640349608</v>
       </c>
       <c r="W45">
-        <v>0.07875</v>
+        <v>0.1302277239196678</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y45">
-        <v>1.507349142190426</v>
+        <v>0.9031213122796863</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1140923026547029</v>
+        <v>0.1151023026547029</v>
       </c>
       <c r="C46">
-        <v>91.54542882936323</v>
+        <v>78.1618380942636</v>
       </c>
       <c r="D46">
-        <v>388.1334288293633</v>
+        <v>382.4768380942637</v>
       </c>
       <c r="E46">
-        <v>-134.612</v>
+        <v>-126.885</v>
       </c>
       <c r="F46">
-        <v>339.988</v>
+        <v>347.715</v>
       </c>
       <c r="G46">
         <v>43.4</v>
@@ -5053,37 +5053,37 @@
         <v>45.075</v>
       </c>
       <c r="M46">
-        <v>49.9102384</v>
+        <v>51.04456200000001</v>
       </c>
       <c r="N46">
-        <v>-4.835238400000009</v>
+        <v>-5.96956200000001</v>
       </c>
       <c r="O46">
-        <v>-0.6044048000000011</v>
+        <v>-0.7461952500000013</v>
       </c>
       <c r="P46">
-        <v>-4.230833600000008</v>
+        <v>-5.223366750000009</v>
       </c>
       <c r="Q46">
-        <v>-3.430833600000003</v>
+        <v>-4.423366750000005</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1014144716608019</v>
+        <v>0.1024256438728165</v>
       </c>
       <c r="T46">
-        <v>0.9377398891528755</v>
+        <v>0.9547897053192913</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1128901640349608</v>
+        <v>0.1103814937230728</v>
       </c>
       <c r="W46">
-        <v>0.1302277239196678</v>
+        <v>0.1305959967214529</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.9031213122796863</v>
+        <v>0.8830519497845821</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1151023026547029</v>
+        <v>0.1161123026547029</v>
       </c>
       <c r="C47">
-        <v>78.1618380942636</v>
+        <v>64.94075538199212</v>
       </c>
       <c r="D47">
-        <v>382.4768380942637</v>
+        <v>376.9827553819922</v>
       </c>
       <c r="E47">
-        <v>-126.885</v>
+        <v>-119.158</v>
       </c>
       <c r="F47">
-        <v>347.715</v>
+        <v>355.4420000000001</v>
       </c>
       <c r="G47">
         <v>43.4</v>
@@ -5135,37 +5135,37 @@
         <v>45.075</v>
       </c>
       <c r="M47">
-        <v>51.04456200000001</v>
+        <v>52.17888560000002</v>
       </c>
       <c r="N47">
-        <v>-5.96956200000001</v>
+        <v>-7.103885600000019</v>
       </c>
       <c r="O47">
-        <v>-0.7461952500000013</v>
+        <v>-0.8879857000000024</v>
       </c>
       <c r="P47">
-        <v>-5.223366750000009</v>
+        <v>-6.215899900000017</v>
       </c>
       <c r="Q47">
-        <v>-4.423366750000005</v>
+        <v>-5.415899900000013</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1024256438728165</v>
+        <v>0.1034742669074983</v>
       </c>
       <c r="T47">
-        <v>0.9547897053192913</v>
+        <v>0.9724709961585375</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1103814937230728</v>
+        <v>0.1079818960334407</v>
       </c>
       <c r="W47">
-        <v>0.1305959967214529</v>
+        <v>0.1309482576622909</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8830519497845821</v>
+        <v>0.8638551682675258</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1161123026547029</v>
+        <v>0.1171223026547029</v>
       </c>
       <c r="C48">
-        <v>64.94075538199212</v>
+        <v>51.87527683091167</v>
       </c>
       <c r="D48">
-        <v>376.9827553819922</v>
+        <v>371.6442768309117</v>
       </c>
       <c r="E48">
-        <v>-119.158</v>
+        <v>-111.431</v>
       </c>
       <c r="F48">
-        <v>355.4420000000001</v>
+        <v>363.169</v>
       </c>
       <c r="G48">
         <v>43.4</v>
@@ -5217,37 +5217,37 @@
         <v>45.075</v>
       </c>
       <c r="M48">
-        <v>52.17888560000002</v>
+        <v>53.31320920000001</v>
       </c>
       <c r="N48">
-        <v>-7.103885600000019</v>
+        <v>-8.238209200000014</v>
       </c>
       <c r="O48">
-        <v>-0.8879857000000024</v>
+        <v>-1.029776150000002</v>
       </c>
       <c r="P48">
-        <v>-6.215899900000017</v>
+        <v>-7.208433050000012</v>
       </c>
       <c r="Q48">
-        <v>-5.415899900000013</v>
+        <v>-6.408433050000008</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1034742669074983</v>
+        <v>0.1045624606227341</v>
       </c>
       <c r="T48">
-        <v>0.9724709961585375</v>
+        <v>0.9908195055200193</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.1079818960334407</v>
+        <v>0.1056844088837931</v>
       </c>
       <c r="W48">
-        <v>0.1309482576622909</v>
+        <v>0.1312855287758592</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8638551682675258</v>
+        <v>0.8454752710703446</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1171223026547029</v>
+        <v>0.1181323026547029</v>
       </c>
       <c r="C49">
-        <v>51.87527683091167</v>
+        <v>38.95888418304986</v>
       </c>
       <c r="D49">
-        <v>371.6442768309117</v>
+        <v>366.45488418305</v>
       </c>
       <c r="E49">
-        <v>-111.431</v>
+        <v>-103.704</v>
       </c>
       <c r="F49">
-        <v>363.169</v>
+        <v>370.8960000000001</v>
       </c>
       <c r="G49">
         <v>43.4</v>
@@ -5299,37 +5299,37 @@
         <v>45.075</v>
       </c>
       <c r="M49">
-        <v>53.31320920000001</v>
+        <v>54.44753280000002</v>
       </c>
       <c r="N49">
-        <v>-8.238209200000014</v>
+        <v>-9.372532800000023</v>
       </c>
       <c r="O49">
-        <v>-1.029776150000002</v>
+        <v>-1.171566600000003</v>
       </c>
       <c r="P49">
-        <v>-7.208433050000012</v>
+        <v>-8.200966200000021</v>
       </c>
       <c r="Q49">
-        <v>-6.408433050000008</v>
+        <v>-7.400966200000017</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1045624606227341</v>
+        <v>0.1056925079424021</v>
       </c>
       <c r="T49">
-        <v>0.9908195055200193</v>
+        <v>1.00987372678002</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1056844088837931</v>
+        <v>0.1034826503653807</v>
       </c>
       <c r="W49">
-        <v>0.1312855287758592</v>
+        <v>0.1316087469263621</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8454752710703446</v>
+        <v>0.8278612029230455</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1181323026547029</v>
+        <v>0.1191423026547029</v>
       </c>
       <c r="C50">
-        <v>38.95888418304992</v>
+        <v>26.18541823327735</v>
       </c>
       <c r="D50">
-        <v>366.45488418305</v>
+        <v>361.4084182332774</v>
       </c>
       <c r="E50">
-        <v>-103.704</v>
+        <v>-95.97700000000003</v>
       </c>
       <c r="F50">
-        <v>370.896</v>
+        <v>378.623</v>
       </c>
       <c r="G50">
         <v>43.4</v>
@@ -5381,37 +5381,37 @@
         <v>45.075</v>
       </c>
       <c r="M50">
-        <v>54.4475328</v>
+        <v>55.58185640000001</v>
       </c>
       <c r="N50">
-        <v>-9.372532800000009</v>
+        <v>-10.50685640000001</v>
       </c>
       <c r="O50">
-        <v>-1.171566600000001</v>
+        <v>-1.313357050000001</v>
       </c>
       <c r="P50">
-        <v>-8.200966200000007</v>
+        <v>-9.19349935000001</v>
       </c>
       <c r="Q50">
-        <v>-7.400966200000003</v>
+        <v>-8.393499350000006</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1056925079424021</v>
+        <v>0.1068668708432335</v>
       </c>
       <c r="T50">
-        <v>1.00987372678002</v>
+        <v>1.029675172403157</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1034826503653807</v>
+        <v>0.1013707595415974</v>
       </c>
       <c r="W50">
-        <v>0.1316087469263621</v>
+        <v>0.1319187724992935</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8278612029230458</v>
+        <v>0.8109660763327795</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1191423026547029</v>
+        <v>0.1475900676179102</v>
       </c>
       <c r="C51">
-        <v>26.18541823327735</v>
+        <v>-82.54614909069392</v>
       </c>
       <c r="D51">
-        <v>361.4084182332774</v>
+        <v>260.4038509093061</v>
       </c>
       <c r="E51">
-        <v>-95.97700000000003</v>
+        <v>-88.25</v>
       </c>
       <c r="F51">
-        <v>378.623</v>
+        <v>386.35</v>
       </c>
       <c r="G51">
         <v>43.4</v>
@@ -5463,45 +5463,45 @@
         <v>45.075</v>
       </c>
       <c r="M51">
-        <v>55.58185640000001</v>
+        <v>77.57908</v>
       </c>
       <c r="N51">
-        <v>-10.50685640000001</v>
+        <v>-32.50408000000001</v>
       </c>
       <c r="O51">
-        <v>-1.313357050000001</v>
+        <v>-4.063010000000001</v>
       </c>
       <c r="P51">
-        <v>-9.19349935000001</v>
+        <v>-28.44107000000001</v>
       </c>
       <c r="Q51">
-        <v>-8.393499350000006</v>
+        <v>-27.64107</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1068668708432335</v>
+        <v>0.1089637381865127</v>
       </c>
       <c r="T51">
-        <v>1.029675172403157</v>
+        <v>1.065031368215781</v>
       </c>
       <c r="U51">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1013707595415974</v>
+        <v>0.07262750473452378</v>
       </c>
       <c r="W51">
-        <v>0.1319187724992935</v>
+        <v>0.1862163970493076</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.8109660763327795</v>
+        <v>0.5810200378761903</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1475900676179102</v>
+        <v>0.1491400676179102</v>
       </c>
       <c r="C52">
-        <v>-82.54614909069392</v>
+        <v>-94.17895231120076</v>
       </c>
       <c r="D52">
-        <v>260.4038509093061</v>
+        <v>256.4980476887993</v>
       </c>
       <c r="E52">
-        <v>-88.25</v>
+        <v>-80.52299999999997</v>
       </c>
       <c r="F52">
-        <v>386.35</v>
+        <v>394.0770000000001</v>
       </c>
       <c r="G52">
         <v>43.4</v>
@@ -5545,37 +5545,37 @@
         <v>45.075</v>
       </c>
       <c r="M52">
-        <v>77.57908</v>
+        <v>79.13066160000001</v>
       </c>
       <c r="N52">
-        <v>-32.50408000000001</v>
+        <v>-34.05566160000001</v>
       </c>
       <c r="O52">
-        <v>-4.063010000000001</v>
+        <v>-4.256957700000002</v>
       </c>
       <c r="P52">
-        <v>-28.44107000000001</v>
+        <v>-29.79870390000001</v>
       </c>
       <c r="Q52">
-        <v>-27.64107</v>
+        <v>-28.99870390000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1089637381865127</v>
+        <v>0.1102527940678701</v>
       </c>
       <c r="T52">
-        <v>1.065031368215781</v>
+        <v>1.086766702261001</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.07262750473452378</v>
+        <v>0.07120343601423899</v>
       </c>
       <c r="W52">
-        <v>0.1862163970493076</v>
+        <v>0.1865023500483408</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5810200378761903</v>
+        <v>0.569627488113912</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1491400676179102</v>
+        <v>0.1506900676179102</v>
       </c>
       <c r="C53">
-        <v>-94.17895231120076</v>
+        <v>-105.6963204837706</v>
       </c>
       <c r="D53">
-        <v>256.4980476887993</v>
+        <v>252.7076795162294</v>
       </c>
       <c r="E53">
-        <v>-80.52299999999997</v>
+        <v>-72.79599999999999</v>
       </c>
       <c r="F53">
-        <v>394.0770000000001</v>
+        <v>401.804</v>
       </c>
       <c r="G53">
         <v>43.4</v>
@@ -5627,37 +5627,37 @@
         <v>45.075</v>
       </c>
       <c r="M53">
-        <v>79.13066160000001</v>
+        <v>80.6822432</v>
       </c>
       <c r="N53">
-        <v>-34.05566160000001</v>
+        <v>-35.60724320000001</v>
       </c>
       <c r="O53">
-        <v>-4.256957700000002</v>
+        <v>-4.450905400000001</v>
       </c>
       <c r="P53">
-        <v>-29.79870390000001</v>
+        <v>-31.15633780000001</v>
       </c>
       <c r="Q53">
-        <v>-28.99870390000001</v>
+        <v>-30.3563378</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1102527940678701</v>
+        <v>0.1115955606109507</v>
       </c>
       <c r="T53">
-        <v>1.086766702261001</v>
+        <v>1.109407675224772</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.07120343601423899</v>
+        <v>0.06983413916781132</v>
       </c>
       <c r="W53">
-        <v>0.1865023500483408</v>
+        <v>0.1867773048551035</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.569627488113912</v>
+        <v>0.5586731133424907</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1506900676179102</v>
+        <v>0.1522400676179101</v>
       </c>
       <c r="C54">
-        <v>-105.6963204837706</v>
+        <v>-117.1032965681173</v>
       </c>
       <c r="D54">
-        <v>252.7076795162294</v>
+        <v>249.0277034318827</v>
       </c>
       <c r="E54">
-        <v>-72.79599999999999</v>
+        <v>-65.06899999999996</v>
       </c>
       <c r="F54">
-        <v>401.804</v>
+        <v>409.5310000000001</v>
       </c>
       <c r="G54">
         <v>43.4</v>
@@ -5709,37 +5709,37 @@
         <v>45.075</v>
       </c>
       <c r="M54">
-        <v>80.6822432</v>
+        <v>82.23382480000002</v>
       </c>
       <c r="N54">
-        <v>-35.60724320000001</v>
+        <v>-37.15882480000003</v>
       </c>
       <c r="O54">
-        <v>-4.450905400000001</v>
+        <v>-4.644853100000003</v>
       </c>
       <c r="P54">
-        <v>-31.15633780000001</v>
+        <v>-32.51397170000002</v>
       </c>
       <c r="Q54">
-        <v>-30.3563378</v>
+        <v>-31.71397170000002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1115955606109507</v>
+        <v>0.1129954661558646</v>
       </c>
       <c r="T54">
-        <v>1.109407675224772</v>
+        <v>1.133012093846575</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.06983413916781132</v>
+        <v>0.06851651390049412</v>
       </c>
       <c r="W54">
-        <v>0.1867773048551035</v>
+        <v>0.1870418840087808</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5586731133424907</v>
+        <v>0.548132111203953</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1522400676179101</v>
+        <v>0.1537900676179102</v>
       </c>
       <c r="C55">
-        <v>-117.1032965681173</v>
+        <v>-128.4046339940845</v>
       </c>
       <c r="D55">
-        <v>249.0277034318827</v>
+        <v>245.4533660059155</v>
       </c>
       <c r="E55">
-        <v>-65.06899999999996</v>
+        <v>-57.34199999999998</v>
       </c>
       <c r="F55">
-        <v>409.5310000000001</v>
+        <v>417.258</v>
       </c>
       <c r="G55">
         <v>43.4</v>
@@ -5791,37 +5791,37 @@
         <v>45.075</v>
       </c>
       <c r="M55">
-        <v>82.23382480000002</v>
+        <v>83.78540640000001</v>
       </c>
       <c r="N55">
-        <v>-37.15882480000003</v>
+        <v>-38.71040640000002</v>
       </c>
       <c r="O55">
-        <v>-4.644853100000003</v>
+        <v>-4.838800800000002</v>
       </c>
       <c r="P55">
-        <v>-32.51397170000002</v>
+        <v>-33.87160560000002</v>
       </c>
       <c r="Q55">
-        <v>-31.71397170000002</v>
+        <v>-33.07160560000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1129954661558646</v>
+        <v>0.1144562371592529</v>
       </c>
       <c r="T55">
-        <v>1.133012093846575</v>
+        <v>1.157642791538892</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.06851651390049412</v>
+        <v>0.0672476895690035</v>
       </c>
       <c r="W55">
-        <v>0.1870418840087808</v>
+        <v>0.1872966639345441</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.548132111203953</v>
+        <v>0.537981516552028</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1537900676179102</v>
+        <v>0.1553400676179102</v>
       </c>
       <c r="C56">
-        <v>-128.4046339940845</v>
+        <v>-139.6048171459905</v>
       </c>
       <c r="D56">
-        <v>245.4533660059155</v>
+        <v>241.9801828540095</v>
       </c>
       <c r="E56">
-        <v>-57.34199999999998</v>
+        <v>-49.61499999999995</v>
       </c>
       <c r="F56">
-        <v>417.258</v>
+        <v>424.9850000000001</v>
       </c>
       <c r="G56">
         <v>43.4</v>
@@ -5873,37 +5873,37 @@
         <v>45.075</v>
       </c>
       <c r="M56">
-        <v>83.78540640000001</v>
+        <v>85.33698800000002</v>
       </c>
       <c r="N56">
-        <v>-38.71040640000002</v>
+        <v>-40.26198800000002</v>
       </c>
       <c r="O56">
-        <v>-4.838800800000002</v>
+        <v>-5.032748500000003</v>
       </c>
       <c r="P56">
-        <v>-33.87160560000002</v>
+        <v>-35.22923950000002</v>
       </c>
       <c r="Q56">
-        <v>-33.07160560000001</v>
+        <v>-34.42923950000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1144562371592529</v>
+        <v>0.1159819313183474</v>
       </c>
       <c r="T56">
-        <v>1.157642791538892</v>
+        <v>1.183368186906423</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.0672476895690035</v>
+        <v>0.06602500430411251</v>
       </c>
       <c r="W56">
-        <v>0.1872966639345441</v>
+        <v>0.1875421791357342</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.537981516552028</v>
+        <v>0.5282000344329001</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1553400676179102</v>
+        <v>0.1568900676179102</v>
       </c>
       <c r="C57">
-        <v>-139.6048171459905</v>
+        <v>-150.7080801321087</v>
       </c>
       <c r="D57">
-        <v>241.9801828540095</v>
+        <v>238.6039198678914</v>
       </c>
       <c r="E57">
-        <v>-49.61499999999995</v>
+        <v>-41.88799999999998</v>
       </c>
       <c r="F57">
-        <v>424.9850000000001</v>
+        <v>432.712</v>
       </c>
       <c r="G57">
         <v>43.4</v>
@@ -5955,37 +5955,37 @@
         <v>45.075</v>
       </c>
       <c r="M57">
-        <v>85.33698800000002</v>
+        <v>86.88856960000001</v>
       </c>
       <c r="N57">
-        <v>-40.26198800000002</v>
+        <v>-41.81356960000002</v>
       </c>
       <c r="O57">
-        <v>-5.032748500000003</v>
+        <v>-5.226696200000002</v>
       </c>
       <c r="P57">
-        <v>-35.22923950000002</v>
+        <v>-36.58687340000002</v>
       </c>
       <c r="Q57">
-        <v>-34.42923950000002</v>
+        <v>-35.78687340000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1159819313183474</v>
+        <v>0.1175769752119462</v>
       </c>
       <c r="T57">
-        <v>1.183368186906423</v>
+        <v>1.210262918427024</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.06602500430411251</v>
+        <v>0.06484598637011052</v>
       </c>
       <c r="W57">
-        <v>0.1875421791357342</v>
+        <v>0.1877789259368818</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5282000344329001</v>
+        <v>0.5187678909608842</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1568900676179102</v>
+        <v>0.1584400676179102</v>
       </c>
       <c r="C58">
-        <v>-150.7080801321087</v>
+        <v>-161.7184240044665</v>
       </c>
       <c r="D58">
-        <v>238.6039198678914</v>
+        <v>235.3205759955336</v>
       </c>
       <c r="E58">
-        <v>-41.88799999999998</v>
+        <v>-34.16099999999994</v>
       </c>
       <c r="F58">
-        <v>432.712</v>
+        <v>440.4390000000001</v>
       </c>
       <c r="G58">
         <v>43.4</v>
@@ -6037,37 +6037,37 @@
         <v>45.075</v>
       </c>
       <c r="M58">
-        <v>86.88856960000001</v>
+        <v>88.44015120000002</v>
       </c>
       <c r="N58">
-        <v>-41.81356960000002</v>
+        <v>-43.36515120000002</v>
       </c>
       <c r="O58">
-        <v>-5.226696200000002</v>
+        <v>-5.420643900000003</v>
       </c>
       <c r="P58">
-        <v>-36.58687340000002</v>
+        <v>-37.94450730000002</v>
       </c>
       <c r="Q58">
-        <v>-35.78687340000001</v>
+        <v>-37.14450730000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1175769752119462</v>
+        <v>0.1192462071936194</v>
       </c>
       <c r="T58">
-        <v>1.210262918427024</v>
+        <v>1.238408567692769</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.06484598637011052</v>
+        <v>0.06370833748642436</v>
       </c>
       <c r="W58">
-        <v>0.1877789259368818</v>
+        <v>0.188007365832726</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5187678909608842</v>
+        <v>0.5096666998913949</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1584400676179102</v>
+        <v>0.1599900676179102</v>
       </c>
       <c r="C59">
-        <v>-161.7184240044665</v>
+        <v>-172.6396325762097</v>
       </c>
       <c r="D59">
-        <v>235.3205759955336</v>
+        <v>232.1263674237903</v>
       </c>
       <c r="E59">
-        <v>-34.16099999999994</v>
+        <v>-26.43399999999997</v>
       </c>
       <c r="F59">
-        <v>440.4390000000001</v>
+        <v>448.1660000000001</v>
       </c>
       <c r="G59">
         <v>43.4</v>
@@ -6119,37 +6119,37 @@
         <v>45.075</v>
       </c>
       <c r="M59">
-        <v>88.44015120000002</v>
+        <v>89.99173280000001</v>
       </c>
       <c r="N59">
-        <v>-43.36515120000002</v>
+        <v>-44.91673280000001</v>
       </c>
       <c r="O59">
-        <v>-5.420643900000003</v>
+        <v>-5.614591600000002</v>
       </c>
       <c r="P59">
-        <v>-37.94450730000002</v>
+        <v>-39.30214120000001</v>
       </c>
       <c r="Q59">
-        <v>-37.14450730000001</v>
+        <v>-38.5021412</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1192462071936194</v>
+        <v>0.1209949264125151</v>
       </c>
       <c r="T59">
-        <v>1.238408567692769</v>
+        <v>1.267894485971168</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.06370833748642436</v>
+        <v>0.06260991787458946</v>
       </c>
       <c r="W59">
-        <v>0.188007365832726</v>
+        <v>0.1882279284907824</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5096666998913949</v>
+        <v>0.5008793429967158</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1599900676179102</v>
+        <v>0.1823667110681786</v>
       </c>
       <c r="C60">
-        <v>-172.6396325762097</v>
+        <v>-218.4008571586195</v>
       </c>
       <c r="D60">
-        <v>232.1263674237903</v>
+        <v>194.0921428413805</v>
       </c>
       <c r="E60">
-        <v>-26.43400000000003</v>
+        <v>-18.70699999999999</v>
       </c>
       <c r="F60">
-        <v>448.166</v>
+        <v>455.893</v>
       </c>
       <c r="G60">
         <v>43.4</v>
@@ -6201,45 +6201,45 @@
         <v>45.075</v>
       </c>
       <c r="M60">
-        <v>89.99173280000001</v>
+        <v>107.4995694</v>
       </c>
       <c r="N60">
-        <v>-44.91673280000001</v>
+        <v>-62.42456940000002</v>
       </c>
       <c r="O60">
-        <v>-5.614591600000002</v>
+        <v>-7.803071175000002</v>
       </c>
       <c r="P60">
-        <v>-39.30214120000001</v>
+        <v>-54.62149822500002</v>
       </c>
       <c r="Q60">
-        <v>-38.5021412</v>
+        <v>-53.82149822500001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1209949264125151</v>
+        <v>0.123259786691524</v>
       </c>
       <c r="T60">
-        <v>1.267894485971168</v>
+        <v>1.306083284022476</v>
       </c>
       <c r="U60">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06260991787458946</v>
+        <v>0.05241300064221466</v>
       </c>
       <c r="W60">
-        <v>0.1882279284907824</v>
+        <v>0.2234410144485658</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.5008793429967158</v>
+        <v>0.4193040051377173</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1823667110681786</v>
+        <v>0.1842667110681787</v>
       </c>
       <c r="C61">
-        <v>-218.4008571586195</v>
+        <v>-228.7911331803707</v>
       </c>
       <c r="D61">
-        <v>194.0921428413805</v>
+        <v>191.4288668196293</v>
       </c>
       <c r="E61">
-        <v>-18.70699999999999</v>
+        <v>-10.98000000000002</v>
       </c>
       <c r="F61">
-        <v>455.893</v>
+        <v>463.62</v>
       </c>
       <c r="G61">
         <v>43.4</v>
@@ -6283,37 +6283,37 @@
         <v>45.075</v>
       </c>
       <c r="M61">
-        <v>107.4995694</v>
+        <v>109.321596</v>
       </c>
       <c r="N61">
-        <v>-62.42456940000002</v>
+        <v>-64.24659600000001</v>
       </c>
       <c r="O61">
-        <v>-7.803071175000002</v>
+        <v>-8.030824500000001</v>
       </c>
       <c r="P61">
-        <v>-54.62149822500002</v>
+        <v>-56.21577150000001</v>
       </c>
       <c r="Q61">
-        <v>-53.82149822500001</v>
+        <v>-55.41577150000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.123259786691524</v>
+        <v>0.1251962813588121</v>
       </c>
       <c r="T61">
-        <v>1.306083284022476</v>
+        <v>1.338735366123038</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05241300064221466</v>
+        <v>0.05153945063151108</v>
       </c>
       <c r="W61">
-        <v>0.2234410144485658</v>
+        <v>0.2236469975410897</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4193040051377173</v>
+        <v>0.4123156050520886</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1842667110681787</v>
+        <v>0.1861667110681787</v>
       </c>
       <c r="C62">
-        <v>-228.7911331803707</v>
+        <v>-239.1093091378998</v>
       </c>
       <c r="D62">
-        <v>191.4288668196293</v>
+        <v>188.8376908621002</v>
       </c>
       <c r="E62">
-        <v>-10.98000000000002</v>
+        <v>-3.252999999999986</v>
       </c>
       <c r="F62">
-        <v>463.62</v>
+        <v>471.347</v>
       </c>
       <c r="G62">
         <v>43.4</v>
@@ -6365,37 +6365,37 @@
         <v>45.075</v>
       </c>
       <c r="M62">
-        <v>109.321596</v>
+        <v>111.1436226</v>
       </c>
       <c r="N62">
-        <v>-64.24659600000001</v>
+        <v>-66.06862260000003</v>
       </c>
       <c r="O62">
-        <v>-8.030824500000001</v>
+        <v>-8.258577825000003</v>
       </c>
       <c r="P62">
-        <v>-56.21577150000001</v>
+        <v>-57.81004477500002</v>
       </c>
       <c r="Q62">
-        <v>-55.41577150000001</v>
+        <v>-57.01004477500002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1251962813588121</v>
+        <v>0.1272320834449355</v>
       </c>
       <c r="T62">
-        <v>1.338735366123038</v>
+        <v>1.373061913972347</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05153945063151108</v>
+        <v>0.05069454160476499</v>
       </c>
       <c r="W62">
-        <v>0.2236469975410897</v>
+        <v>0.2238462270895964</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4123156050520886</v>
+        <v>0.4055563328381199</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1861667110681787</v>
+        <v>0.1880667110681787</v>
       </c>
       <c r="C63">
-        <v>-239.1093091378998</v>
+        <v>-249.3582737629627</v>
       </c>
       <c r="D63">
-        <v>188.8376908621002</v>
+        <v>186.3157262370373</v>
       </c>
       <c r="E63">
-        <v>-3.252999999999986</v>
+        <v>4.47399999999999</v>
       </c>
       <c r="F63">
-        <v>471.347</v>
+        <v>479.074</v>
       </c>
       <c r="G63">
         <v>43.4</v>
@@ -6447,37 +6447,37 @@
         <v>45.075</v>
       </c>
       <c r="M63">
-        <v>111.1436226</v>
+        <v>112.9656492</v>
       </c>
       <c r="N63">
-        <v>-66.06862260000003</v>
+        <v>-67.89064920000001</v>
       </c>
       <c r="O63">
-        <v>-8.258577825000003</v>
+        <v>-8.486331150000002</v>
       </c>
       <c r="P63">
-        <v>-57.81004477500002</v>
+        <v>-59.40431805000001</v>
       </c>
       <c r="Q63">
-        <v>-57.01004477500002</v>
+        <v>-58.60431805000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1272320834449355</v>
+        <v>0.1293750330092759</v>
       </c>
       <c r="T63">
-        <v>1.373061913972347</v>
+        <v>1.409195122234777</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05069454160476499</v>
+        <v>0.04987688770791395</v>
       </c>
       <c r="W63">
-        <v>0.2238462270895964</v>
+        <v>0.2240390298784739</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4055563328381199</v>
+        <v>0.3990151016633116</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1880667110681787</v>
+        <v>0.1899667110681787</v>
       </c>
       <c r="C64">
-        <v>-249.3582737629627</v>
+        <v>-259.5407635027748</v>
       </c>
       <c r="D64">
-        <v>186.3157262370373</v>
+        <v>183.8602364972252</v>
       </c>
       <c r="E64">
-        <v>4.47399999999999</v>
+        <v>12.20100000000002</v>
       </c>
       <c r="F64">
-        <v>479.074</v>
+        <v>486.801</v>
       </c>
       <c r="G64">
         <v>43.4</v>
@@ -6529,37 +6529,37 @@
         <v>45.075</v>
       </c>
       <c r="M64">
-        <v>112.9656492</v>
+        <v>114.7876758</v>
       </c>
       <c r="N64">
-        <v>-67.89064920000001</v>
+        <v>-69.71267580000003</v>
       </c>
       <c r="O64">
-        <v>-8.486331150000002</v>
+        <v>-8.714084475000003</v>
       </c>
       <c r="P64">
-        <v>-59.40431805000001</v>
+        <v>-60.99859132500002</v>
       </c>
       <c r="Q64">
-        <v>-58.60431805000001</v>
+        <v>-60.19859132500002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1293750330092759</v>
+        <v>0.1316338176852023</v>
       </c>
       <c r="T64">
-        <v>1.409195122234777</v>
+        <v>1.447281476889771</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04987688770791395</v>
+        <v>0.0490851910776296</v>
       </c>
       <c r="W64">
-        <v>0.2240390298784739</v>
+        <v>0.224225711943895</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3990151016633116</v>
+        <v>0.3926815286210367</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1899667110681787</v>
+        <v>0.1918667110681787</v>
       </c>
       <c r="C65">
-        <v>-259.5407635027748</v>
+        <v>-269.6593724244111</v>
       </c>
       <c r="D65">
-        <v>183.8602364972252</v>
+        <v>181.4686275755889</v>
       </c>
       <c r="E65">
-        <v>12.20100000000002</v>
+        <v>19.928</v>
       </c>
       <c r="F65">
-        <v>486.801</v>
+        <v>494.528</v>
       </c>
       <c r="G65">
         <v>43.4</v>
@@ -6611,37 +6611,37 @@
         <v>45.075</v>
       </c>
       <c r="M65">
-        <v>114.7876758</v>
+        <v>116.6097024</v>
       </c>
       <c r="N65">
-        <v>-69.71267580000003</v>
+        <v>-71.53470240000001</v>
       </c>
       <c r="O65">
-        <v>-8.714084475000003</v>
+        <v>-8.941837800000002</v>
       </c>
       <c r="P65">
-        <v>-60.99859132500002</v>
+        <v>-62.59286460000001</v>
       </c>
       <c r="Q65">
-        <v>-60.19859132500002</v>
+        <v>-61.79286460000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1316338176852023</v>
+        <v>0.1340180903986801</v>
       </c>
       <c r="T65">
-        <v>1.447281476889771</v>
+        <v>1.487483740136709</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0490851910776296</v>
+        <v>0.04831823496704164</v>
       </c>
       <c r="W65">
-        <v>0.224225711943895</v>
+        <v>0.2244065601947716</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3926815286210367</v>
+        <v>0.386545879736333</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1918667110681787</v>
+        <v>0.1937667110681787</v>
       </c>
       <c r="C66">
-        <v>-269.6593724244111</v>
+        <v>-279.716561356128</v>
       </c>
       <c r="D66">
-        <v>181.4686275755889</v>
+        <v>179.1384386438721</v>
       </c>
       <c r="E66">
-        <v>19.928</v>
+        <v>27.65500000000003</v>
       </c>
       <c r="F66">
-        <v>494.528</v>
+        <v>502.2550000000001</v>
       </c>
       <c r="G66">
         <v>43.4</v>
@@ -6693,37 +6693,37 @@
         <v>45.075</v>
       </c>
       <c r="M66">
-        <v>116.6097024</v>
+        <v>118.431729</v>
       </c>
       <c r="N66">
-        <v>-71.53470240000001</v>
+        <v>-73.35672900000003</v>
       </c>
       <c r="O66">
-        <v>-8.941837800000002</v>
+        <v>-9.169591125000004</v>
       </c>
       <c r="P66">
-        <v>-62.59286460000001</v>
+        <v>-64.18713787500002</v>
       </c>
       <c r="Q66">
-        <v>-61.79286460000001</v>
+        <v>-63.38713787500001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1340180903986801</v>
+        <v>0.1365386072672139</v>
       </c>
       <c r="T66">
-        <v>1.487483740136709</v>
+        <v>1.529983275569186</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04831823496704164</v>
+        <v>0.04757487750601022</v>
       </c>
       <c r="W66">
-        <v>0.2244065601947716</v>
+        <v>0.2245818438840828</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.386545879736333</v>
+        <v>0.3805990200480818</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1937667110681787</v>
+        <v>0.1956667110681787</v>
       </c>
       <c r="C67">
-        <v>-279.716561356128</v>
+        <v>-289.7146663333268</v>
       </c>
       <c r="D67">
-        <v>179.1384386438721</v>
+        <v>176.8673336666732</v>
       </c>
       <c r="E67">
-        <v>27.65500000000003</v>
+        <v>35.38200000000001</v>
       </c>
       <c r="F67">
-        <v>502.2550000000001</v>
+        <v>509.982</v>
       </c>
       <c r="G67">
         <v>43.4</v>
@@ -6775,37 +6775,37 @@
         <v>45.075</v>
       </c>
       <c r="M67">
-        <v>118.431729</v>
+        <v>120.2537556</v>
       </c>
       <c r="N67">
-        <v>-73.35672900000003</v>
+        <v>-75.17875560000002</v>
       </c>
       <c r="O67">
-        <v>-9.169591125000004</v>
+        <v>-9.397344450000002</v>
       </c>
       <c r="P67">
-        <v>-64.18713787500002</v>
+        <v>-65.78141115000001</v>
       </c>
       <c r="Q67">
-        <v>-63.38713787500001</v>
+        <v>-64.98141115000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1365386072672139</v>
+        <v>0.1392073898338966</v>
       </c>
       <c r="T67">
-        <v>1.529983275569186</v>
+        <v>1.574982783674162</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04757487750601022</v>
+        <v>0.04685404602864644</v>
       </c>
       <c r="W67">
-        <v>0.2245818438840828</v>
+        <v>0.2247518159464452</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3805990200480818</v>
+        <v>0.3748323682291714</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1956667110681787</v>
+        <v>0.1975667110681787</v>
       </c>
       <c r="C68">
-        <v>-289.7146663333268</v>
+        <v>-299.6559064100965</v>
       </c>
       <c r="D68">
-        <v>176.8673336666732</v>
+        <v>174.6530935899036</v>
       </c>
       <c r="E68">
-        <v>35.38200000000001</v>
+        <v>43.10900000000004</v>
       </c>
       <c r="F68">
-        <v>509.982</v>
+        <v>517.7090000000001</v>
       </c>
       <c r="G68">
         <v>43.4</v>
@@ -6857,37 +6857,37 @@
         <v>45.075</v>
       </c>
       <c r="M68">
-        <v>120.2537556</v>
+        <v>122.0757822</v>
       </c>
       <c r="N68">
-        <v>-75.17875560000002</v>
+        <v>-77.00078220000003</v>
       </c>
       <c r="O68">
-        <v>-9.397344450000002</v>
+        <v>-9.625097775000004</v>
       </c>
       <c r="P68">
-        <v>-65.78141115000001</v>
+        <v>-67.37568442500003</v>
       </c>
       <c r="Q68">
-        <v>-64.98141115000001</v>
+        <v>-66.57568442500002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1392073898338966</v>
+        <v>0.1420379167985601</v>
       </c>
       <c r="T68">
-        <v>1.574982783674162</v>
+        <v>1.622709534694591</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04685404602864644</v>
+        <v>0.04615473190881589</v>
       </c>
       <c r="W68">
-        <v>0.2247518159464452</v>
+        <v>0.2249167142159012</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3748323682291714</v>
+        <v>0.369237855270527</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1975667110681787</v>
+        <v>0.1994667110681786</v>
       </c>
       <c r="C69">
-        <v>-299.6559064100965</v>
+        <v>-309.5423908912446</v>
       </c>
       <c r="D69">
-        <v>174.6530935899036</v>
+        <v>172.4936091087554</v>
       </c>
       <c r="E69">
-        <v>43.10900000000004</v>
+        <v>50.83600000000001</v>
       </c>
       <c r="F69">
-        <v>517.7090000000001</v>
+        <v>525.436</v>
       </c>
       <c r="G69">
         <v>43.4</v>
@@ -6939,37 +6939,37 @@
         <v>45.075</v>
       </c>
       <c r="M69">
-        <v>122.0757822</v>
+        <v>123.8978088</v>
       </c>
       <c r="N69">
-        <v>-77.00078220000003</v>
+        <v>-78.82280880000002</v>
       </c>
       <c r="O69">
-        <v>-9.625097775000004</v>
+        <v>-9.852851100000002</v>
       </c>
       <c r="P69">
-        <v>-67.37568442500003</v>
+        <v>-68.96995770000001</v>
       </c>
       <c r="Q69">
-        <v>-66.57568442500002</v>
+        <v>-68.1699577</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1420379167985601</v>
+        <v>0.1450453516985152</v>
       </c>
       <c r="T69">
-        <v>1.622709534694591</v>
+        <v>1.673419207653797</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04615473190881589</v>
+        <v>0.04547598585133331</v>
       </c>
       <c r="W69">
-        <v>0.2249167142159012</v>
+        <v>0.2250767625362556</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.369237855270527</v>
+        <v>0.3638078868106663</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1994667110681786</v>
+        <v>0.2013667110681787</v>
       </c>
       <c r="C70">
-        <v>-309.5423908912446</v>
+        <v>-319.3761260343628</v>
       </c>
       <c r="D70">
-        <v>172.4936091087554</v>
+        <v>170.3868739656373</v>
       </c>
       <c r="E70">
-        <v>50.83600000000001</v>
+        <v>58.5630000000001</v>
       </c>
       <c r="F70">
-        <v>525.436</v>
+        <v>533.1630000000001</v>
       </c>
       <c r="G70">
         <v>43.4</v>
@@ -7021,37 +7021,37 @@
         <v>45.075</v>
       </c>
       <c r="M70">
-        <v>123.8978088</v>
+        <v>125.7198354</v>
       </c>
       <c r="N70">
-        <v>-78.82280880000002</v>
+        <v>-80.64483540000003</v>
       </c>
       <c r="O70">
-        <v>-9.852851100000002</v>
+        <v>-10.080604425</v>
       </c>
       <c r="P70">
-        <v>-68.96995770000001</v>
+        <v>-70.56423097500003</v>
       </c>
       <c r="Q70">
-        <v>-68.1699577</v>
+        <v>-69.76423097500003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1450453516985152</v>
+        <v>0.1482468146565318</v>
       </c>
       <c r="T70">
-        <v>1.673419207653797</v>
+        <v>1.727400472416823</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04547598585133331</v>
+        <v>0.04481691359261832</v>
       </c>
       <c r="W70">
-        <v>0.2250767625362556</v>
+        <v>0.2252321717748606</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3638078868106663</v>
+        <v>0.3585353087409466</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2013667110681787</v>
+        <v>0.2032667110681787</v>
       </c>
       <c r="C71">
-        <v>-319.3761260343628</v>
+        <v>-329.1590212666862</v>
       </c>
       <c r="D71">
-        <v>170.3868739656373</v>
+        <v>168.3309787333139</v>
       </c>
       <c r="E71">
-        <v>58.5630000000001</v>
+        <v>66.29000000000008</v>
       </c>
       <c r="F71">
-        <v>533.1630000000001</v>
+        <v>540.8900000000001</v>
       </c>
       <c r="G71">
         <v>43.4</v>
@@ -7103,37 +7103,37 @@
         <v>45.075</v>
       </c>
       <c r="M71">
-        <v>125.7198354</v>
+        <v>127.541862</v>
       </c>
       <c r="N71">
-        <v>-80.64483540000003</v>
+        <v>-82.46686200000002</v>
       </c>
       <c r="O71">
-        <v>-10.080604425</v>
+        <v>-10.30835775</v>
       </c>
       <c r="P71">
-        <v>-70.56423097500003</v>
+        <v>-72.15850425000002</v>
       </c>
       <c r="Q71">
-        <v>-69.76423097500003</v>
+        <v>-71.35850425000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1482468146565318</v>
+        <v>0.1516617084784162</v>
       </c>
       <c r="T71">
-        <v>1.727400472416823</v>
+        <v>1.784980488164051</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04481691359261832</v>
+        <v>0.04417667196986663</v>
       </c>
       <c r="W71">
-        <v>0.2252321717748606</v>
+        <v>0.2253831407495055</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3585353087409466</v>
+        <v>0.3534133757589332</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2032667110681787</v>
+        <v>0.2051667110681787</v>
       </c>
       <c r="C72">
-        <v>-329.1590212666862</v>
+        <v>-338.892894957243</v>
       </c>
       <c r="D72">
-        <v>168.3309787333139</v>
+        <v>166.3241050427571</v>
       </c>
       <c r="E72">
-        <v>66.29000000000008</v>
+        <v>74.01700000000005</v>
       </c>
       <c r="F72">
-        <v>540.8900000000001</v>
+        <v>548.6170000000001</v>
       </c>
       <c r="G72">
         <v>43.4</v>
@@ -7185,37 +7185,37 @@
         <v>45.075</v>
       </c>
       <c r="M72">
-        <v>127.541862</v>
+        <v>129.3638886</v>
       </c>
       <c r="N72">
-        <v>-82.46686200000002</v>
+        <v>-84.28888860000004</v>
       </c>
       <c r="O72">
-        <v>-10.30835775</v>
+        <v>-10.536111075</v>
       </c>
       <c r="P72">
-        <v>-72.15850425000002</v>
+        <v>-73.75277752500003</v>
       </c>
       <c r="Q72">
-        <v>-71.35850425000001</v>
+        <v>-72.95277752500002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1516617084784162</v>
+        <v>0.1553121122190512</v>
       </c>
       <c r="T72">
-        <v>1.784980488164051</v>
+        <v>1.846531539480053</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04417667196986663</v>
+        <v>0.04355446532240372</v>
       </c>
       <c r="W72">
-        <v>0.2253831407495055</v>
+        <v>0.2255298570769772</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3534133757589332</v>
+        <v>0.3484357225792297</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2051667110681787</v>
+        <v>0.2070667110681787</v>
       </c>
       <c r="C73">
-        <v>-338.8928949572428</v>
+        <v>-348.5794797809679</v>
       </c>
       <c r="D73">
-        <v>166.3241050427571</v>
+        <v>164.3645202190322</v>
       </c>
       <c r="E73">
-        <v>74.01699999999994</v>
+        <v>81.74400000000003</v>
       </c>
       <c r="F73">
-        <v>548.617</v>
+        <v>556.3440000000001</v>
       </c>
       <c r="G73">
         <v>43.4</v>
@@ -7267,37 +7267,37 @@
         <v>45.075</v>
       </c>
       <c r="M73">
-        <v>129.3638886</v>
+        <v>131.1859152</v>
       </c>
       <c r="N73">
-        <v>-84.28888860000001</v>
+        <v>-86.11091520000002</v>
       </c>
       <c r="O73">
-        <v>-10.536111075</v>
+        <v>-10.7638644</v>
       </c>
       <c r="P73">
-        <v>-73.752777525</v>
+        <v>-75.34705080000002</v>
       </c>
       <c r="Q73">
-        <v>-72.95277752499999</v>
+        <v>-74.54705080000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1553121122190512</v>
+        <v>0.1592232590840173</v>
       </c>
       <c r="T73">
-        <v>1.846531539480052</v>
+        <v>1.912479094461482</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04355446532240374</v>
+        <v>0.0429495421929259</v>
       </c>
       <c r="W73">
-        <v>0.2255298570769772</v>
+        <v>0.2256724979509081</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3484357225792298</v>
+        <v>0.3435963375434071</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2070667110681787</v>
+        <v>0.2089667110681787</v>
       </c>
       <c r="C74">
-        <v>-348.5794797809679</v>
+        <v>-358.2204277080402</v>
       </c>
       <c r="D74">
-        <v>164.3645202190322</v>
+        <v>162.4505722919598</v>
       </c>
       <c r="E74">
-        <v>81.74400000000003</v>
+        <v>89.471</v>
       </c>
       <c r="F74">
-        <v>556.3440000000001</v>
+        <v>564.071</v>
       </c>
       <c r="G74">
         <v>43.4</v>
@@ -7349,37 +7349,37 @@
         <v>45.075</v>
       </c>
       <c r="M74">
-        <v>131.1859152</v>
+        <v>133.0079418</v>
       </c>
       <c r="N74">
-        <v>-86.11091520000002</v>
+        <v>-87.93294180000001</v>
       </c>
       <c r="O74">
-        <v>-10.7638644</v>
+        <v>-10.991617725</v>
       </c>
       <c r="P74">
-        <v>-75.34705080000002</v>
+        <v>-76.94132407500001</v>
       </c>
       <c r="Q74">
-        <v>-74.54705080000002</v>
+        <v>-76.141324075</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1592232590840173</v>
+        <v>0.1634241205315735</v>
       </c>
       <c r="T74">
-        <v>1.912479094461482</v>
+        <v>1.983311653515611</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0429495421929259</v>
+        <v>0.04236119229987213</v>
       </c>
       <c r="W74">
-        <v>0.2256724979509081</v>
+        <v>0.2258112308556902</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3435963375434071</v>
+        <v>0.338889538398977</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2089667110681787</v>
+        <v>0.2108667110681787</v>
       </c>
       <c r="C75">
-        <v>-358.2204277080402</v>
+        <v>-367.8173146486436</v>
       </c>
       <c r="D75">
-        <v>162.4505722919598</v>
+        <v>160.5806853513564</v>
       </c>
       <c r="E75">
-        <v>89.471</v>
+        <v>97.19799999999998</v>
       </c>
       <c r="F75">
-        <v>564.071</v>
+        <v>571.798</v>
       </c>
       <c r="G75">
         <v>43.4</v>
@@ -7431,37 +7431,37 @@
         <v>45.075</v>
       </c>
       <c r="M75">
-        <v>133.0079418</v>
+        <v>134.8299684</v>
       </c>
       <c r="N75">
-        <v>-87.93294180000001</v>
+        <v>-89.75496840000002</v>
       </c>
       <c r="O75">
-        <v>-10.991617725</v>
+        <v>-11.21937105</v>
       </c>
       <c r="P75">
-        <v>-76.94132407500001</v>
+        <v>-78.53559735000002</v>
       </c>
       <c r="Q75">
-        <v>-76.141324075</v>
+        <v>-77.73559735000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1634241205315735</v>
+        <v>0.1679481251674032</v>
       </c>
       <c r="T75">
-        <v>1.983311653515611</v>
+        <v>2.059592870958519</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04236119229987213</v>
+        <v>0.04178874375527925</v>
       </c>
       <c r="W75">
-        <v>0.2258112308556902</v>
+        <v>0.2259462142225052</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.338889538398977</v>
+        <v>0.334309950042234</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2108667110681787</v>
+        <v>0.2127667110681787</v>
       </c>
       <c r="C76">
-        <v>-367.8173146486436</v>
+        <v>-377.3716447805943</v>
       </c>
       <c r="D76">
-        <v>160.5806853513564</v>
+        <v>158.7533552194058</v>
       </c>
       <c r="E76">
-        <v>97.19799999999998</v>
+        <v>104.9250000000001</v>
       </c>
       <c r="F76">
-        <v>571.798</v>
+        <v>579.5250000000001</v>
       </c>
       <c r="G76">
         <v>43.4</v>
@@ -7513,37 +7513,37 @@
         <v>45.075</v>
       </c>
       <c r="M76">
-        <v>134.8299684</v>
+        <v>136.651995</v>
       </c>
       <c r="N76">
-        <v>-89.75496840000002</v>
+        <v>-91.57699500000004</v>
       </c>
       <c r="O76">
-        <v>-11.21937105</v>
+        <v>-11.447124375</v>
       </c>
       <c r="P76">
-        <v>-78.53559735000002</v>
+        <v>-80.12987062500004</v>
       </c>
       <c r="Q76">
-        <v>-77.73559735000001</v>
+        <v>-79.32987062500004</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1679481251674032</v>
+        <v>0.1728340501740994</v>
       </c>
       <c r="T76">
-        <v>2.059592870958519</v>
+        <v>2.14197658579686</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04178874375527925</v>
+        <v>0.04123156050520886</v>
       </c>
       <c r="W76">
-        <v>0.2259462142225052</v>
+        <v>0.2260775980328718</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.334309950042234</v>
+        <v>0.3298524840416708</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2127667110681787</v>
+        <v>0.2146667110681787</v>
       </c>
       <c r="C77">
-        <v>-377.3716447805943</v>
+        <v>-386.8848545848173</v>
       </c>
       <c r="D77">
-        <v>158.7533552194058</v>
+        <v>156.9671454151828</v>
       </c>
       <c r="E77">
-        <v>104.9250000000001</v>
+        <v>112.652</v>
       </c>
       <c r="F77">
-        <v>579.5250000000001</v>
+        <v>587.2520000000001</v>
       </c>
       <c r="G77">
         <v>43.4</v>
@@ -7595,37 +7595,37 @@
         <v>45.075</v>
       </c>
       <c r="M77">
-        <v>136.651995</v>
+        <v>138.4740216</v>
       </c>
       <c r="N77">
-        <v>-91.57699500000004</v>
+        <v>-93.39902160000003</v>
       </c>
       <c r="O77">
-        <v>-11.447124375</v>
+        <v>-11.6748777</v>
       </c>
       <c r="P77">
-        <v>-80.12987062500004</v>
+        <v>-81.72414390000003</v>
       </c>
       <c r="Q77">
-        <v>-79.32987062500004</v>
+        <v>-80.92414390000002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1728340501740994</v>
+        <v>0.1781271355980202</v>
       </c>
       <c r="T77">
-        <v>2.14197658579686</v>
+        <v>2.231225610205063</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04123156050520886</v>
+        <v>0.04068903997224559</v>
       </c>
       <c r="W77">
-        <v>0.2260775980328718</v>
+        <v>0.2262055243745445</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3298524840416708</v>
+        <v>0.3255123197779647</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2146667110681787</v>
+        <v>0.2165667110681787</v>
       </c>
       <c r="C78">
-        <v>-386.8848545848173</v>
+        <v>-396.3583166114224</v>
       </c>
       <c r="D78">
-        <v>156.9671454151828</v>
+        <v>155.2206833885776</v>
       </c>
       <c r="E78">
-        <v>112.652</v>
+        <v>120.379</v>
       </c>
       <c r="F78">
-        <v>587.2520000000001</v>
+        <v>594.979</v>
       </c>
       <c r="G78">
         <v>43.4</v>
@@ -7677,37 +7677,37 @@
         <v>45.075</v>
       </c>
       <c r="M78">
-        <v>138.4740216</v>
+        <v>140.2960482</v>
       </c>
       <c r="N78">
-        <v>-93.39902160000003</v>
+        <v>-95.22104820000004</v>
       </c>
       <c r="O78">
-        <v>-11.6748777</v>
+        <v>-11.90263102500001</v>
       </c>
       <c r="P78">
-        <v>-81.72414390000003</v>
+        <v>-83.31841717500004</v>
       </c>
       <c r="Q78">
-        <v>-80.92414390000002</v>
+        <v>-82.51841717500002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1781271355980202</v>
+        <v>0.1838804893196732</v>
       </c>
       <c r="T78">
-        <v>2.231225610205063</v>
+        <v>2.328235419344414</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04068903997224559</v>
+        <v>0.04016061088169694</v>
       </c>
       <c r="W78">
-        <v>0.2262055243745445</v>
+        <v>0.2263301279540958</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3255123197779647</v>
+        <v>0.3212848870535755</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2165667110681787</v>
+        <v>0.2184667110681787</v>
       </c>
       <c r="C79">
-        <v>-396.3583166114224</v>
+        <v>-405.793342997133</v>
       </c>
       <c r="D79">
-        <v>155.2206833885776</v>
+        <v>153.5126570028671</v>
       </c>
       <c r="E79">
-        <v>120.379</v>
+        <v>128.106</v>
       </c>
       <c r="F79">
-        <v>594.979</v>
+        <v>602.706</v>
       </c>
       <c r="G79">
         <v>43.4</v>
@@ -7759,37 +7759,37 @@
         <v>45.075</v>
       </c>
       <c r="M79">
-        <v>140.2960482</v>
+        <v>142.1180748</v>
       </c>
       <c r="N79">
-        <v>-95.22104820000004</v>
+        <v>-97.04307480000003</v>
       </c>
       <c r="O79">
-        <v>-11.90263102500001</v>
+        <v>-12.13038435</v>
       </c>
       <c r="P79">
-        <v>-83.31841717500004</v>
+        <v>-84.91269045000003</v>
       </c>
       <c r="Q79">
-        <v>-82.51841717500002</v>
+        <v>-84.11269045000003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1838804893196732</v>
+        <v>0.1901568751978402</v>
       </c>
       <c r="T79">
-        <v>2.328235419344414</v>
+        <v>2.434064302041887</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04016061088169694</v>
+        <v>0.03964573125500852</v>
       </c>
       <c r="W79">
-        <v>0.2263301279540958</v>
+        <v>0.226451536570069</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3212848870535755</v>
+        <v>0.3171658500400681</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2184667110681787</v>
+        <v>0.2203667110681787</v>
       </c>
       <c r="C80">
-        <v>-405.793342997133</v>
+        <v>-415.1911887530088</v>
       </c>
       <c r="D80">
-        <v>153.5126570028671</v>
+        <v>151.8418112469914</v>
       </c>
       <c r="E80">
-        <v>128.106</v>
+        <v>135.8330000000001</v>
       </c>
       <c r="F80">
-        <v>602.706</v>
+        <v>610.4330000000001</v>
       </c>
       <c r="G80">
         <v>43.4</v>
@@ -7841,37 +7841,37 @@
         <v>45.075</v>
       </c>
       <c r="M80">
-        <v>142.1180748</v>
+        <v>143.9401014</v>
       </c>
       <c r="N80">
-        <v>-97.04307480000003</v>
+        <v>-98.86510140000004</v>
       </c>
       <c r="O80">
-        <v>-12.13038435</v>
+        <v>-12.35813767500001</v>
       </c>
       <c r="P80">
-        <v>-84.91269045000003</v>
+        <v>-86.50696372500003</v>
       </c>
       <c r="Q80">
-        <v>-84.11269045000003</v>
+        <v>-85.70696372500004</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1901568751978402</v>
+        <v>0.1970310121120231</v>
       </c>
       <c r="T80">
-        <v>2.434064302041887</v>
+        <v>2.549972125948644</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03964573125500852</v>
+        <v>0.03914388655557803</v>
       </c>
       <c r="W80">
-        <v>0.226451536570069</v>
+        <v>0.2265698715501947</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3171658500400681</v>
+        <v>0.3131510924446241</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2203667110681787</v>
+        <v>0.2222667110681787</v>
       </c>
       <c r="C81">
-        <v>-415.1911887530088</v>
+        <v>-424.5530548397792</v>
       </c>
       <c r="D81">
-        <v>151.8418112469914</v>
+        <v>150.2069451602209</v>
       </c>
       <c r="E81">
-        <v>135.8330000000001</v>
+        <v>143.5600000000001</v>
       </c>
       <c r="F81">
-        <v>610.4330000000001</v>
+        <v>618.1600000000001</v>
       </c>
       <c r="G81">
         <v>43.4</v>
@@ -7923,37 +7923,37 @@
         <v>45.075</v>
       </c>
       <c r="M81">
-        <v>143.9401014</v>
+        <v>145.762128</v>
       </c>
       <c r="N81">
-        <v>-98.86510140000004</v>
+        <v>-100.687128</v>
       </c>
       <c r="O81">
-        <v>-12.35813767500001</v>
+        <v>-12.585891</v>
       </c>
       <c r="P81">
-        <v>-86.50696372500003</v>
+        <v>-88.10123700000003</v>
       </c>
       <c r="Q81">
-        <v>-85.70696372500004</v>
+        <v>-87.30123700000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1970310121120231</v>
+        <v>0.2045925627176243</v>
       </c>
       <c r="T81">
-        <v>2.549972125948644</v>
+        <v>2.677470732246076</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03914388655557803</v>
+        <v>0.03865458797363331</v>
       </c>
       <c r="W81">
-        <v>0.2265698715501947</v>
+        <v>0.2266852481558173</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3131510924446241</v>
+        <v>0.3092367037890664</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2222667110681787</v>
+        <v>0.2241667110681787</v>
       </c>
       <c r="C82">
-        <v>-424.5530548397792</v>
+        <v>-433.8800910466211</v>
       </c>
       <c r="D82">
-        <v>150.2069451602209</v>
+        <v>148.6069089533789</v>
       </c>
       <c r="E82">
-        <v>143.5600000000001</v>
+        <v>151.287</v>
       </c>
       <c r="F82">
-        <v>618.1600000000001</v>
+        <v>625.8870000000001</v>
       </c>
       <c r="G82">
         <v>43.4</v>
@@ -8005,37 +8005,37 @@
         <v>45.075</v>
       </c>
       <c r="M82">
-        <v>145.762128</v>
+        <v>147.5841546</v>
       </c>
       <c r="N82">
-        <v>-100.687128</v>
+        <v>-102.5091546</v>
       </c>
       <c r="O82">
-        <v>-12.585891</v>
+        <v>-12.81364432500001</v>
       </c>
       <c r="P82">
-        <v>-88.10123700000003</v>
+        <v>-89.69551027500003</v>
       </c>
       <c r="Q82">
-        <v>-87.30123700000001</v>
+        <v>-88.89551027500002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2045925627176243</v>
+        <v>0.2129500660185519</v>
       </c>
       <c r="T82">
-        <v>2.677470732246076</v>
+        <v>2.818390244469554</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03865458797363331</v>
+        <v>0.03817737083815635</v>
       </c>
       <c r="W82">
-        <v>0.2266852481558173</v>
+        <v>0.2267977759563627</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3092367037890664</v>
+        <v>0.3054189667052507</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2241667110681787</v>
+        <v>0.2260667110681787</v>
       </c>
       <c r="C83">
-        <v>-433.8800910466211</v>
+        <v>-443.1733986878841</v>
       </c>
       <c r="D83">
-        <v>148.6069089533789</v>
+        <v>147.0406013121159</v>
       </c>
       <c r="E83">
-        <v>151.287</v>
+        <v>159.014</v>
       </c>
       <c r="F83">
-        <v>625.8870000000001</v>
+        <v>633.614</v>
       </c>
       <c r="G83">
         <v>43.4</v>
@@ -8087,37 +8087,37 @@
         <v>45.075</v>
       </c>
       <c r="M83">
-        <v>147.5841546</v>
+        <v>149.4061812</v>
       </c>
       <c r="N83">
-        <v>-102.5091546</v>
+        <v>-104.3311812</v>
       </c>
       <c r="O83">
-        <v>-12.81364432500001</v>
+        <v>-13.04139765</v>
       </c>
       <c r="P83">
-        <v>-89.69551027500003</v>
+        <v>-91.28978355000002</v>
       </c>
       <c r="Q83">
-        <v>-88.89551027500002</v>
+        <v>-90.48978355000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2129500660185519</v>
+        <v>0.2222361807973603</v>
       </c>
       <c r="T83">
-        <v>2.818390244469554</v>
+        <v>2.974967480273418</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03817737083815635</v>
+        <v>0.0377117931450081</v>
       </c>
       <c r="W83">
-        <v>0.2267977759563627</v>
+        <v>0.2269075591764071</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3054189667052507</v>
+        <v>0.3016943451600648</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2260667110681787</v>
+        <v>0.2279667110681787</v>
       </c>
       <c r="C84">
-        <v>-443.1733986878841</v>
+        <v>-452.4340331310534</v>
       </c>
       <c r="D84">
-        <v>147.0406013121159</v>
+        <v>145.5069668689468</v>
       </c>
       <c r="E84">
-        <v>159.014</v>
+        <v>166.7410000000001</v>
       </c>
       <c r="F84">
-        <v>633.614</v>
+        <v>641.3410000000001</v>
       </c>
       <c r="G84">
         <v>43.4</v>
@@ -8169,37 +8169,37 @@
         <v>45.075</v>
       </c>
       <c r="M84">
-        <v>149.4061812</v>
+        <v>151.2282078</v>
       </c>
       <c r="N84">
-        <v>-104.3311812</v>
+        <v>-106.1532078</v>
       </c>
       <c r="O84">
-        <v>-13.04139765</v>
+        <v>-13.26915097500001</v>
       </c>
       <c r="P84">
-        <v>-91.28978355000002</v>
+        <v>-92.88405682500004</v>
       </c>
       <c r="Q84">
-        <v>-90.48978355000003</v>
+        <v>-92.08405682500003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2222361807973603</v>
+        <v>0.2326147796677933</v>
       </c>
       <c r="T84">
-        <v>2.974967480273418</v>
+        <v>3.149965567348325</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0377117931450081</v>
+        <v>0.03725743419145379</v>
       </c>
       <c r="W84">
-        <v>0.2269075591764071</v>
+        <v>0.2270146970176552</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3016943451600648</v>
+        <v>0.2980594735316302</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2279667110681787</v>
+        <v>0.2298667110681787</v>
       </c>
       <c r="C85">
-        <v>-452.4340331310534</v>
+        <v>-461.6630061681475</v>
       </c>
       <c r="D85">
-        <v>145.5069668689468</v>
+        <v>144.0049938318526</v>
       </c>
       <c r="E85">
-        <v>166.7410000000001</v>
+        <v>174.4680000000001</v>
       </c>
       <c r="F85">
-        <v>641.3410000000001</v>
+        <v>649.0680000000001</v>
       </c>
       <c r="G85">
         <v>43.4</v>
@@ -8251,37 +8251,37 @@
         <v>45.075</v>
       </c>
       <c r="M85">
-        <v>151.2282078</v>
+        <v>153.0502344</v>
       </c>
       <c r="N85">
-        <v>-106.1532078</v>
+        <v>-107.9752344</v>
       </c>
       <c r="O85">
-        <v>-13.26915097500001</v>
+        <v>-13.4969043</v>
       </c>
       <c r="P85">
-        <v>-92.88405682500004</v>
+        <v>-94.47833010000002</v>
       </c>
       <c r="Q85">
-        <v>-92.08405682500003</v>
+        <v>-93.67833010000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2326147796677933</v>
+        <v>0.2442907033970304</v>
       </c>
       <c r="T85">
-        <v>3.149965567348325</v>
+        <v>3.346838415307596</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03725743419145379</v>
+        <v>0.0368138933082222</v>
       </c>
       <c r="W85">
-        <v>0.2270146970176552</v>
+        <v>0.2271192839579212</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2980594735316302</v>
+        <v>0.2945111464657775</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2298667110681787</v>
+        <v>0.2317667110681787</v>
       </c>
       <c r="C86">
-        <v>-461.6630061681473</v>
+        <v>-470.8612882417451</v>
       </c>
       <c r="D86">
-        <v>144.0049938318527</v>
+        <v>142.533711758255</v>
       </c>
       <c r="E86">
-        <v>174.468</v>
+        <v>182.1950000000001</v>
       </c>
       <c r="F86">
-        <v>649.068</v>
+        <v>656.7950000000001</v>
       </c>
       <c r="G86">
         <v>43.4</v>
@@ -8333,37 +8333,37 @@
         <v>45.075</v>
       </c>
       <c r="M86">
-        <v>153.0502344</v>
+        <v>154.872261</v>
       </c>
       <c r="N86">
-        <v>-107.9752344</v>
+        <v>-109.797261</v>
       </c>
       <c r="O86">
-        <v>-13.4969043</v>
+        <v>-13.72465762500001</v>
       </c>
       <c r="P86">
-        <v>-94.47833010000001</v>
+        <v>-96.07260337500004</v>
       </c>
       <c r="Q86">
-        <v>-93.67833010000001</v>
+        <v>-95.27260337500005</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2442907033970303</v>
+        <v>0.2575234169568323</v>
       </c>
       <c r="T86">
-        <v>3.346838415307595</v>
+        <v>3.569960976328101</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03681389330822221</v>
+        <v>0.03638078868106664</v>
       </c>
       <c r="W86">
-        <v>0.2271192839579212</v>
+        <v>0.2272214100290045</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2945111464657776</v>
+        <v>0.291046309448533</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2317667110681787</v>
+        <v>0.2336667110681787</v>
       </c>
       <c r="C87">
-        <v>-470.8612882417451</v>
+        <v>-480.0298105359338</v>
       </c>
       <c r="D87">
-        <v>142.533711758255</v>
+        <v>141.0921894640663</v>
       </c>
       <c r="E87">
-        <v>182.1950000000001</v>
+        <v>189.922</v>
       </c>
       <c r="F87">
-        <v>656.7950000000001</v>
+        <v>664.522</v>
       </c>
       <c r="G87">
         <v>43.4</v>
@@ -8415,37 +8415,37 @@
         <v>45.075</v>
       </c>
       <c r="M87">
-        <v>154.872261</v>
+        <v>156.6942876</v>
       </c>
       <c r="N87">
-        <v>-109.797261</v>
+        <v>-111.6192876</v>
       </c>
       <c r="O87">
-        <v>-13.72465762500001</v>
+        <v>-13.95241095</v>
       </c>
       <c r="P87">
-        <v>-96.07260337500004</v>
+        <v>-97.66687665000003</v>
       </c>
       <c r="Q87">
-        <v>-95.27260337500005</v>
+        <v>-96.86687665000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2575234169568323</v>
+        <v>0.2726465181680346</v>
       </c>
       <c r="T87">
-        <v>3.569960976328101</v>
+        <v>3.824958188922965</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03638078868106664</v>
+        <v>0.03595775625454261</v>
       </c>
       <c r="W87">
-        <v>0.2272214100290045</v>
+        <v>0.2273211610751789</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.291046309448533</v>
+        <v>0.2876620500363408</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2336667110681787</v>
+        <v>0.2355667110681786</v>
       </c>
       <c r="C88">
-        <v>-480.0298105359338</v>
+        <v>-489.1694669416476</v>
       </c>
       <c r="D88">
-        <v>141.0921894640663</v>
+        <v>139.6795330583524</v>
       </c>
       <c r="E88">
-        <v>189.922</v>
+        <v>197.649</v>
       </c>
       <c r="F88">
-        <v>664.522</v>
+        <v>672.249</v>
       </c>
       <c r="G88">
         <v>43.4</v>
@@ -8497,37 +8497,37 @@
         <v>45.075</v>
       </c>
       <c r="M88">
-        <v>156.6942876</v>
+        <v>158.5163142</v>
       </c>
       <c r="N88">
-        <v>-111.6192876</v>
+        <v>-113.4413142</v>
       </c>
       <c r="O88">
-        <v>-13.95241095</v>
+        <v>-14.180164275</v>
       </c>
       <c r="P88">
-        <v>-97.66687665000003</v>
+        <v>-99.26114992500001</v>
       </c>
       <c r="Q88">
-        <v>-96.86687665000002</v>
+        <v>-98.461149925</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2726465181680346</v>
+        <v>0.2900962503348065</v>
       </c>
       <c r="T88">
-        <v>3.824958188922965</v>
+        <v>4.119185741917039</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03595775625454261</v>
+        <v>0.03554444871138695</v>
       </c>
       <c r="W88">
-        <v>0.2273211610751789</v>
+        <v>0.227418618993855</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2876620500363408</v>
+        <v>0.2843555896910955</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2355667110681786</v>
+        <v>0.2374667110681787</v>
       </c>
       <c r="C89">
-        <v>-489.1694669416476</v>
+        <v>-498.2811159051104</v>
       </c>
       <c r="D89">
-        <v>139.6795330583524</v>
+        <v>138.2948840948896</v>
       </c>
       <c r="E89">
-        <v>197.649</v>
+        <v>205.376</v>
       </c>
       <c r="F89">
-        <v>672.249</v>
+        <v>679.976</v>
       </c>
       <c r="G89">
         <v>43.4</v>
@@ -8579,37 +8579,37 @@
         <v>45.075</v>
       </c>
       <c r="M89">
-        <v>158.5163142</v>
+        <v>160.3383408</v>
       </c>
       <c r="N89">
-        <v>-113.4413142</v>
+        <v>-115.2633408</v>
       </c>
       <c r="O89">
-        <v>-14.180164275</v>
+        <v>-14.4079176</v>
       </c>
       <c r="P89">
-        <v>-99.26114992500001</v>
+        <v>-100.8554232</v>
       </c>
       <c r="Q89">
-        <v>-98.461149925</v>
+        <v>-100.0554232</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2900962503348065</v>
+        <v>0.3104542711960404</v>
       </c>
       <c r="T89">
-        <v>4.119185741917039</v>
+        <v>4.462451220410126</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03554444871138695</v>
+        <v>0.03514053452148483</v>
       </c>
       <c r="W89">
-        <v>0.227418618993855</v>
+        <v>0.2275138619598339</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2843555896910955</v>
+        <v>0.2811242761718786</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2374667110681787</v>
+        <v>0.2393667110681787</v>
       </c>
       <c r="C90">
-        <v>-498.2811159051104</v>
+        <v>-507.3655821674149</v>
       </c>
       <c r="D90">
-        <v>138.2948840948896</v>
+        <v>136.9374178325852</v>
       </c>
       <c r="E90">
-        <v>205.376</v>
+        <v>213.1030000000001</v>
       </c>
       <c r="F90">
-        <v>679.976</v>
+        <v>687.7030000000001</v>
       </c>
       <c r="G90">
         <v>43.4</v>
@@ -8661,37 +8661,37 @@
         <v>45.075</v>
       </c>
       <c r="M90">
-        <v>160.3383408</v>
+        <v>162.1603674</v>
       </c>
       <c r="N90">
-        <v>-115.2633408</v>
+        <v>-117.0853674000001</v>
       </c>
       <c r="O90">
-        <v>-14.4079176</v>
+        <v>-14.63567092500001</v>
       </c>
       <c r="P90">
-        <v>-100.8554232</v>
+        <v>-102.4496964750001</v>
       </c>
       <c r="Q90">
-        <v>-100.0554232</v>
+        <v>-101.649696475</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3104542711960404</v>
+        <v>0.3345137503956805</v>
       </c>
       <c r="T90">
-        <v>4.462451220410126</v>
+        <v>4.868128604083775</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03514053452148483</v>
+        <v>0.03474569705495129</v>
       </c>
       <c r="W90">
-        <v>0.2275138619598339</v>
+        <v>0.2276069646344425</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2811242761718786</v>
+        <v>0.2779655764396102</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2393667110681787</v>
+        <v>0.2412667110681787</v>
       </c>
       <c r="C91">
-        <v>-507.3655821674149</v>
+        <v>-516.4236584026474</v>
       </c>
       <c r="D91">
-        <v>136.9374178325852</v>
+        <v>135.6063415973526</v>
       </c>
       <c r="E91">
-        <v>213.1030000000001</v>
+        <v>220.83</v>
       </c>
       <c r="F91">
-        <v>687.7030000000001</v>
+        <v>695.4300000000001</v>
       </c>
       <c r="G91">
         <v>43.4</v>
@@ -8743,37 +8743,37 @@
         <v>45.075</v>
       </c>
       <c r="M91">
-        <v>162.1603674</v>
+        <v>163.982394</v>
       </c>
       <c r="N91">
-        <v>-117.0853674000001</v>
+        <v>-118.907394</v>
       </c>
       <c r="O91">
-        <v>-14.63567092500001</v>
+        <v>-14.86342425</v>
       </c>
       <c r="P91">
-        <v>-102.4496964750001</v>
+        <v>-104.04396975</v>
       </c>
       <c r="Q91">
-        <v>-101.649696475</v>
+        <v>-103.24396975</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3345137503956805</v>
+        <v>0.3633851254352485</v>
       </c>
       <c r="T91">
-        <v>4.868128604083775</v>
+        <v>5.354941464492152</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03474569705495129</v>
+        <v>0.03435963375434072</v>
       </c>
       <c r="W91">
-        <v>0.2276069646344425</v>
+        <v>0.2276979983607265</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2779655764396102</v>
+        <v>0.2748770700347257</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2412667110681787</v>
+        <v>0.2431667110681787</v>
       </c>
       <c r="C92">
-        <v>-516.4236584026474</v>
+        <v>-525.456106761393</v>
       </c>
       <c r="D92">
-        <v>135.6063415973526</v>
+        <v>134.300893238607</v>
       </c>
       <c r="E92">
-        <v>220.83</v>
+        <v>228.557</v>
       </c>
       <c r="F92">
-        <v>695.4300000000001</v>
+        <v>703.157</v>
       </c>
       <c r="G92">
         <v>43.4</v>
@@ -8825,37 +8825,37 @@
         <v>45.075</v>
       </c>
       <c r="M92">
-        <v>163.982394</v>
+        <v>165.8044206</v>
       </c>
       <c r="N92">
-        <v>-118.907394</v>
+        <v>-120.7294206</v>
       </c>
       <c r="O92">
-        <v>-14.86342425</v>
+        <v>-15.091177575</v>
       </c>
       <c r="P92">
-        <v>-104.04396975</v>
+        <v>-105.638243025</v>
       </c>
       <c r="Q92">
-        <v>-103.24396975</v>
+        <v>-104.838243025</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3633851254352485</v>
+        <v>0.3986723615947206</v>
       </c>
       <c r="T92">
-        <v>5.354941464492152</v>
+        <v>5.949934960546837</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03435963375434072</v>
+        <v>0.03398205536143588</v>
       </c>
       <c r="W92">
-        <v>0.2276979983607265</v>
+        <v>0.2277870313457734</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2748770700347257</v>
+        <v>0.2718564428914869</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2431667110681787</v>
+        <v>0.2450667110681787</v>
       </c>
       <c r="C93">
-        <v>-525.456106761393</v>
+        <v>-534.4636603259373</v>
       </c>
       <c r="D93">
-        <v>134.300893238607</v>
+        <v>133.0203396740629</v>
       </c>
       <c r="E93">
-        <v>228.557</v>
+        <v>236.2840000000001</v>
       </c>
       <c r="F93">
-        <v>703.157</v>
+        <v>710.8840000000001</v>
       </c>
       <c r="G93">
         <v>43.4</v>
@@ -8907,37 +8907,37 @@
         <v>45.075</v>
       </c>
       <c r="M93">
-        <v>165.8044206</v>
+        <v>167.6264472</v>
       </c>
       <c r="N93">
-        <v>-120.7294206</v>
+        <v>-122.5514472</v>
       </c>
       <c r="O93">
-        <v>-15.091177575</v>
+        <v>-15.31893090000001</v>
       </c>
       <c r="P93">
-        <v>-105.638243025</v>
+        <v>-107.2325163</v>
       </c>
       <c r="Q93">
-        <v>-104.838243025</v>
+        <v>-106.4325163</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3986723615947206</v>
+        <v>0.4427814067940608</v>
       </c>
       <c r="T93">
-        <v>5.949934960546837</v>
+        <v>6.693676830615193</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03398205536143588</v>
+        <v>0.03361268519446375</v>
       </c>
       <c r="W93">
-        <v>0.2277870313457734</v>
+        <v>0.2278741288311455</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2718564428914869</v>
+        <v>0.2689014815557099</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2450667110681787</v>
+        <v>0.2469667110681787</v>
       </c>
       <c r="C94">
-        <v>-534.4636603259373</v>
+        <v>-543.4470244830023</v>
       </c>
       <c r="D94">
-        <v>133.0203396740629</v>
+        <v>131.7639755169978</v>
       </c>
       <c r="E94">
-        <v>236.2840000000001</v>
+        <v>244.0110000000001</v>
       </c>
       <c r="F94">
-        <v>710.8840000000001</v>
+        <v>718.6110000000001</v>
       </c>
       <c r="G94">
         <v>43.4</v>
@@ -8989,37 +8989,37 @@
         <v>45.075</v>
       </c>
       <c r="M94">
-        <v>167.6264472</v>
+        <v>169.4484738</v>
       </c>
       <c r="N94">
-        <v>-122.5514472</v>
+        <v>-124.3734738000001</v>
       </c>
       <c r="O94">
-        <v>-15.31893090000001</v>
+        <v>-15.54668422500001</v>
       </c>
       <c r="P94">
-        <v>-107.2325163</v>
+        <v>-108.826789575</v>
       </c>
       <c r="Q94">
-        <v>-106.4325163</v>
+        <v>-108.026789575</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4427814067940608</v>
+        <v>0.4994930363360696</v>
       </c>
       <c r="T94">
-        <v>6.693676830615193</v>
+        <v>7.649916377845936</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03361268519446375</v>
+        <v>0.03325125847194262</v>
       </c>
       <c r="W94">
-        <v>0.2278741288311455</v>
+        <v>0.2279593532523159</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2689014815557099</v>
+        <v>0.2660100677755409</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2469667110681787</v>
+        <v>0.2488667110681786</v>
       </c>
       <c r="C95">
-        <v>-543.4470244830023</v>
+        <v>-552.4068782194191</v>
       </c>
       <c r="D95">
-        <v>131.7639755169978</v>
+        <v>130.5311217805809</v>
       </c>
       <c r="E95">
-        <v>244.0110000000001</v>
+        <v>251.7380000000001</v>
       </c>
       <c r="F95">
-        <v>718.6110000000001</v>
+        <v>726.3380000000001</v>
       </c>
       <c r="G95">
         <v>43.4</v>
@@ -9071,37 +9071,37 @@
         <v>45.075</v>
       </c>
       <c r="M95">
-        <v>169.4484738</v>
+        <v>171.2705004</v>
       </c>
       <c r="N95">
-        <v>-124.3734738000001</v>
+        <v>-126.1955004</v>
       </c>
       <c r="O95">
-        <v>-15.54668422500001</v>
+        <v>-15.77443755000001</v>
       </c>
       <c r="P95">
-        <v>-108.826789575</v>
+        <v>-110.42106285</v>
       </c>
       <c r="Q95">
-        <v>-108.026789575</v>
+        <v>-109.62106285</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4994930363360696</v>
+        <v>0.5751085423920812</v>
       </c>
       <c r="T95">
-        <v>7.649916377845936</v>
+        <v>8.92490244082026</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03325125847194262</v>
+        <v>0.03289752167968792</v>
       </c>
       <c r="W95">
-        <v>0.2279593532523159</v>
+        <v>0.2280427643879296</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2660100677755409</v>
+        <v>0.2631801734375033</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2488667110681786</v>
+        <v>0.2507667110681787</v>
       </c>
       <c r="C96">
-        <v>-552.4068782194191</v>
+        <v>-561.3438753457359</v>
       </c>
       <c r="D96">
-        <v>130.5311217805809</v>
+        <v>129.3211246542641</v>
       </c>
       <c r="E96">
-        <v>251.7380000000001</v>
+        <v>259.465</v>
       </c>
       <c r="F96">
-        <v>726.3380000000001</v>
+        <v>734.0650000000001</v>
       </c>
       <c r="G96">
         <v>43.4</v>
@@ -9153,37 +9153,37 @@
         <v>45.075</v>
       </c>
       <c r="M96">
-        <v>171.2705004</v>
+        <v>173.092527</v>
       </c>
       <c r="N96">
-        <v>-126.1955004</v>
+        <v>-128.017527</v>
       </c>
       <c r="O96">
-        <v>-15.77443755000001</v>
+        <v>-16.002190875</v>
       </c>
       <c r="P96">
-        <v>-110.42106285</v>
+        <v>-112.015336125</v>
       </c>
       <c r="Q96">
-        <v>-109.62106285</v>
+        <v>-111.215336125</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5751085423920812</v>
+        <v>0.6809702508704977</v>
       </c>
       <c r="T96">
-        <v>8.92490244082026</v>
+        <v>10.70988292898432</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03289752167968792</v>
+        <v>0.03255123197779647</v>
       </c>
       <c r="W96">
-        <v>0.2280427643879296</v>
+        <v>0.2281244194996356</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2631801734375033</v>
+        <v>0.2604098558223717</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2507667110681787</v>
+        <v>0.2526667110681787</v>
       </c>
       <c r="C97">
-        <v>-561.3438753457359</v>
+        <v>-570.2586456523956</v>
       </c>
       <c r="D97">
-        <v>129.3211246542641</v>
+        <v>128.1333543476046</v>
       </c>
       <c r="E97">
-        <v>259.465</v>
+        <v>267.1920000000001</v>
       </c>
       <c r="F97">
-        <v>734.0650000000001</v>
+        <v>741.7920000000001</v>
       </c>
       <c r="G97">
         <v>43.4</v>
@@ -9235,37 +9235,37 @@
         <v>45.075</v>
       </c>
       <c r="M97">
-        <v>173.092527</v>
+        <v>174.9145536</v>
       </c>
       <c r="N97">
-        <v>-128.017527</v>
+        <v>-129.8395536</v>
       </c>
       <c r="O97">
-        <v>-16.002190875</v>
+        <v>-16.22994420000001</v>
       </c>
       <c r="P97">
-        <v>-112.015336125</v>
+        <v>-113.6096094</v>
       </c>
       <c r="Q97">
-        <v>-111.215336125</v>
+        <v>-112.8096094</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6809702508704977</v>
+        <v>0.8397628135881225</v>
       </c>
       <c r="T97">
-        <v>10.70988292898432</v>
+        <v>13.3873536612304</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03255123197779647</v>
+        <v>0.03221215664469442</v>
       </c>
       <c r="W97">
-        <v>0.2281244194996356</v>
+        <v>0.2282043734631811</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2604098558223717</v>
+        <v>0.2576972531575553</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2526667110681787</v>
+        <v>0.2545667110681787</v>
       </c>
       <c r="C98">
-        <v>-570.2586456523954</v>
+        <v>-579.1517960027784</v>
       </c>
       <c r="D98">
-        <v>128.1333543476046</v>
+        <v>126.9672039972216</v>
       </c>
       <c r="E98">
-        <v>267.192</v>
+        <v>274.919</v>
       </c>
       <c r="F98">
-        <v>741.792</v>
+        <v>749.519</v>
       </c>
       <c r="G98">
         <v>43.4</v>
@@ -9317,37 +9317,37 @@
         <v>45.075</v>
       </c>
       <c r="M98">
-        <v>174.9145536</v>
+        <v>176.7365802</v>
       </c>
       <c r="N98">
-        <v>-129.8395536</v>
+        <v>-131.6615802</v>
       </c>
       <c r="O98">
-        <v>-16.2299442</v>
+        <v>-16.457697525</v>
       </c>
       <c r="P98">
-        <v>-113.6096094</v>
+        <v>-115.203882675</v>
       </c>
       <c r="Q98">
-        <v>-112.8096094</v>
+        <v>-114.403882675</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8397628135881203</v>
+        <v>1.104417084784161</v>
       </c>
       <c r="T98">
-        <v>13.38735366123037</v>
+        <v>17.84980488164049</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03221215664469443</v>
+        <v>0.03188007255557386</v>
       </c>
       <c r="W98">
-        <v>0.2282043734631811</v>
+        <v>0.2282826788913957</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2576972531575553</v>
+        <v>0.2550405804445909</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2545667110681787</v>
+        <v>0.2564667110681786</v>
       </c>
       <c r="C99">
-        <v>-579.1517960027784</v>
+        <v>-588.0239113670973</v>
       </c>
       <c r="D99">
-        <v>126.9672039972216</v>
+        <v>125.8220886329026</v>
       </c>
       <c r="E99">
-        <v>274.919</v>
+        <v>282.646</v>
       </c>
       <c r="F99">
-        <v>749.519</v>
+        <v>757.246</v>
       </c>
       <c r="G99">
         <v>43.4</v>
@@ -9399,37 +9399,37 @@
         <v>45.075</v>
       </c>
       <c r="M99">
-        <v>176.7365802</v>
+        <v>178.5586068</v>
       </c>
       <c r="N99">
-        <v>-131.6615802</v>
+        <v>-133.4836068</v>
       </c>
       <c r="O99">
-        <v>-16.457697525</v>
+        <v>-16.68545085</v>
       </c>
       <c r="P99">
-        <v>-115.203882675</v>
+        <v>-116.79815595</v>
       </c>
       <c r="Q99">
-        <v>-114.403882675</v>
+        <v>-115.99815595</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.104417084784161</v>
+        <v>1.633725627176241</v>
       </c>
       <c r="T99">
-        <v>17.84980488164049</v>
+        <v>26.77470732246073</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03188007255557386</v>
+        <v>0.03155476569276189</v>
       </c>
       <c r="W99">
-        <v>0.2282826788913957</v>
+        <v>0.2283593862496467</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2550405804445909</v>
+        <v>0.2524381255420951</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2564667110681786</v>
+        <v>0.2583667110681787</v>
       </c>
       <c r="C100">
-        <v>-588.0239113670973</v>
+        <v>-596.8755558008434</v>
       </c>
       <c r="D100">
-        <v>125.8220886329026</v>
+        <v>124.6974441991566</v>
       </c>
       <c r="E100">
-        <v>282.646</v>
+        <v>290.373</v>
       </c>
       <c r="F100">
-        <v>757.246</v>
+        <v>764.9730000000001</v>
       </c>
       <c r="G100">
         <v>43.4</v>
@@ -9481,37 +9481,37 @@
         <v>45.075</v>
       </c>
       <c r="M100">
-        <v>178.5586068</v>
+        <v>180.3806334</v>
       </c>
       <c r="N100">
-        <v>-133.4836068</v>
+        <v>-135.3056334</v>
       </c>
       <c r="O100">
-        <v>-16.68545085</v>
+        <v>-16.913204175</v>
       </c>
       <c r="P100">
-        <v>-116.79815595</v>
+        <v>-118.392429225</v>
       </c>
       <c r="Q100">
-        <v>-115.99815595</v>
+        <v>-117.592429225</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.633725627176241</v>
+        <v>3.221651254352481</v>
       </c>
       <c r="T100">
-        <v>26.77470732246073</v>
+        <v>53.54941464492146</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03155476569276189</v>
+        <v>0.03123603068576429</v>
       </c>
       <c r="W100">
-        <v>0.2283593862496467</v>
+        <v>0.2284345439642968</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2524381255420951</v>
+        <v>0.2498882454861143</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2583667110681787</v>
-      </c>
-      <c r="C101">
-        <v>-596.8755558008434</v>
-      </c>
-      <c r="D101">
-        <v>124.6974441991566</v>
-      </c>
-      <c r="E101">
-        <v>290.373</v>
-      </c>
-      <c r="F101">
-        <v>764.9730000000001</v>
-      </c>
-      <c r="G101">
-        <v>43.4</v>
-      </c>
-      <c r="H101">
-        <v>298.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>45.875</v>
-      </c>
-      <c r="K101">
-        <v>0.8000000000000043</v>
-      </c>
-      <c r="L101">
-        <v>45.075</v>
-      </c>
-      <c r="M101">
-        <v>180.3806334</v>
-      </c>
-      <c r="N101">
-        <v>-135.3056334</v>
-      </c>
-      <c r="O101">
-        <v>-16.913204175</v>
-      </c>
-      <c r="P101">
-        <v>-118.392429225</v>
-      </c>
-      <c r="Q101">
-        <v>-117.592429225</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.221651254352481</v>
-      </c>
-      <c r="T101">
-        <v>53.54941464492146</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03123603068576429</v>
-      </c>
-      <c r="W101">
-        <v>0.2284345439642968</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2498882454861143</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
